--- a/database/event/2239/event_2239_evp_summary.xlsx
+++ b/database/event/2239/event_2239_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0186</v>
+        <v>7.656</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4765</v>
+        <v>2.7014</v>
       </c>
       <c r="D2" t="n">
-        <v>2.414</v>
+        <v>2.6062</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0186</v>
+        <v>7.656</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8242</v>
+        <v>3.4617</v>
       </c>
       <c r="G2" t="n">
         <v>4.1943</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8242</v>
+        <v>3.4617</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2891</v>
+        <v>2.8058</v>
       </c>
       <c r="J2" t="n">
         <v>4.1943</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4834</v>
+        <v>7.0001</v>
       </c>
       <c r="N2" t="n">
         <v>229</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7779</v>
+        <v>5.4209</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6859</v>
+        <v>1.9128</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5088</v>
+        <v>1.7158</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7779</v>
+        <v>5.4209</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7631</v>
+        <v>2.4061</v>
       </c>
       <c r="G3" t="n">
         <v>3.0148</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7631</v>
+        <v>2.4061</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4291</v>
+        <v>1.9502</v>
       </c>
       <c r="J3" t="n">
         <v>3.0148</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4439</v>
+        <v>4.965</v>
       </c>
       <c r="N3" t="n">
         <v>308</v>
@@ -584,47 +584,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9989</v>
+        <v>4.7559</v>
       </c>
       <c r="C4" t="n">
-        <v>1.411</v>
+        <v>1.6781</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1941</v>
+        <v>1.4508</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9989</v>
+        <v>4.7559</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7303</v>
+        <v>3.8208</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2686</v>
+        <v>0.9351</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7303</v>
+        <v>3.8208</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4024</v>
+        <v>3.0969</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2686</v>
+        <v>0.9351</v>
       </c>
       <c r="K4" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="L4" t="n">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.671</v>
+        <v>4.032</v>
       </c>
       <c r="N4" t="n">
-        <v>308</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5">
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9628</v>
+        <v>4.5102</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3983</v>
+        <v>1.5914</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1795</v>
+        <v>1.353</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9628</v>
+        <v>4.5102</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1514</v>
+        <v>3.6988</v>
       </c>
       <c r="G5" t="n">
         <v>0.8114</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1514</v>
+        <v>3.6988</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5543</v>
+        <v>2.998</v>
       </c>
       <c r="J5" t="n">
         <v>0.8114</v>
@@ -667,7 +667,7 @@
         <v>157</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3657</v>
+        <v>3.8094</v>
       </c>
       <c r="N5" t="n">
         <v>229</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8941</v>
+        <v>4.2979</v>
       </c>
       <c r="C6" t="n">
-        <v>1.374</v>
+        <v>1.5165</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1518</v>
+        <v>1.2684</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8941</v>
+        <v>4.2979</v>
       </c>
       <c r="F6" t="n">
-        <v>2.959</v>
+        <v>3.2003</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9351</v>
+        <v>1.0976</v>
       </c>
       <c r="H6" t="n">
-        <v>2.959</v>
+        <v>3.2003</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3984</v>
+        <v>2.5939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9351</v>
+        <v>1.0976</v>
       </c>
       <c r="K6" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="L6" t="n">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3335</v>
+        <v>3.6915</v>
       </c>
       <c r="N6" t="n">
-        <v>208</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7906</v>
+        <v>4.2159</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3375</v>
+        <v>1.4876</v>
       </c>
       <c r="D7" t="n">
-        <v>1.11</v>
+        <v>1.2357</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7906</v>
+        <v>4.2159</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9106</v>
+        <v>1.9473</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88</v>
+        <v>2.2686</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9106</v>
+        <v>1.9473</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5486</v>
+        <v>1.5783</v>
       </c>
       <c r="J7" t="n">
-        <v>1.88</v>
+        <v>2.2686</v>
       </c>
       <c r="K7" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="L7" t="n">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4286</v>
+        <v>3.8469</v>
       </c>
       <c r="N7" t="n">
-        <v>229</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5676</v>
+        <v>4.0905</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2588</v>
+        <v>1.4433</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0199</v>
+        <v>1.1857</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5676</v>
+        <v>4.0905</v>
       </c>
       <c r="F8" t="n">
-        <v>2.47</v>
+        <v>2.2104</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0976</v>
+        <v>1.88</v>
       </c>
       <c r="H8" t="n">
-        <v>2.47</v>
+        <v>2.2104</v>
       </c>
       <c r="I8" t="n">
-        <v>2.002</v>
+        <v>1.7916</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0976</v>
+        <v>1.88</v>
       </c>
       <c r="K8" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="L8" t="n">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0996</v>
+        <v>3.6716</v>
       </c>
       <c r="N8" t="n">
-        <v>308</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7982</v>
+        <v>3.5314</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9874000000000001</v>
+        <v>1.2461</v>
       </c>
       <c r="D9" t="n">
-        <v>0.709</v>
+        <v>0.963</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7982</v>
+        <v>3.5314</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5015</v>
+        <v>4.2347</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7033</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5015</v>
+        <v>4.4767</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8381</v>
+        <v>3.6285</v>
       </c>
       <c r="J9" t="n">
         <v>-0.7033</v>
@@ -851,7 +851,7 @@
         <v>104</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1348</v>
+        <v>2.9252</v>
       </c>
       <c r="N9" t="n">
         <v>205</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3115</v>
+        <v>2.5944</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8156</v>
+        <v>0.9154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5124</v>
+        <v>0.5897</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3115</v>
+        <v>2.5944</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1257</v>
+        <v>2.4086</v>
       </c>
       <c r="G10" t="n">
         <v>0.1858</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1257</v>
+        <v>2.4086</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7229</v>
+        <v>1.9522</v>
       </c>
       <c r="J10" t="n">
         <v>0.1858</v>
@@ -897,7 +897,7 @@
         <v>104</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9087</v>
+        <v>2.138</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0256</v>
+        <v>2.2189</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7147</v>
+        <v>0.7829</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3969</v>
+        <v>0.4401</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0256</v>
+        <v>2.2189</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6712</v>
+        <v>1.8645</v>
       </c>
       <c r="G11" t="n">
         <v>0.3544</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6712</v>
+        <v>1.8645</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3545</v>
+        <v>1.5112</v>
       </c>
       <c r="J11" t="n">
         <v>0.3544</v>
@@ -943,7 +943,7 @@
         <v>104</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7089</v>
+        <v>1.8656</v>
       </c>
       <c r="N11" t="n">
         <v>205</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.97</v>
+        <v>2.0873</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7365</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3745</v>
+        <v>0.3877</v>
       </c>
       <c r="E12" t="n">
-        <v>1.97</v>
+        <v>2.0873</v>
       </c>
       <c r="F12" t="n">
-        <v>1.97</v>
+        <v>2.0873</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.97</v>
+        <v>2.0873</v>
       </c>
       <c r="I12" t="n">
-        <v>1.97</v>
+        <v>2.0873</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.97</v>
+        <v>2.0873</v>
       </c>
       <c r="N12" t="n">
         <v>126</v>
@@ -998,216 +998,216 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.386</v>
+        <v>2.0505</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4891</v>
+        <v>0.7235</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1386</v>
+        <v>0.373</v>
       </c>
       <c r="E13" t="n">
-        <v>1.386</v>
+        <v>2.0505</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2161</v>
+        <v>2.0505</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1699</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2161</v>
+        <v>2.0505</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1752</v>
+        <v>2.0505</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1699</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L13" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3451</v>
+        <v>2.0505</v>
       </c>
       <c r="N13" t="n">
-        <v>308</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2584</v>
+        <v>1.5859</v>
       </c>
       <c r="C14" t="n">
-        <v>0.444</v>
+        <v>0.5596</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1879</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2584</v>
+        <v>1.5859</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2584</v>
+        <v>0.416</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.1699</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2584</v>
+        <v>0.416</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2584</v>
+        <v>0.3372</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.1699</v>
       </c>
       <c r="K14" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2584</v>
+        <v>1.5071</v>
       </c>
       <c r="N14" t="n">
-        <v>126</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1238</v>
+        <v>1.4388</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3965</v>
+        <v>0.5077</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0326</v>
+        <v>0.1293</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1238</v>
+        <v>1.4388</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1238</v>
+        <v>1.4388</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1238</v>
+        <v>1.4388</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1238</v>
+        <v>1.4388</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1238</v>
+        <v>1.4388</v>
       </c>
       <c r="N15" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9107</v>
+        <v>1.229</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3213</v>
+        <v>0.4337</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0535</v>
+        <v>0.0457</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9107</v>
+        <v>1.229</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6532</v>
+        <v>1.229</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2575</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6532</v>
+        <v>1.229</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5294</v>
+        <v>1.229</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2575</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="L16" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7868999999999999</v>
+        <v>1.229</v>
       </c>
       <c r="N16" t="n">
-        <v>208</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8396</v>
+        <v>1.0498</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2963</v>
+        <v>0.3704</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0822</v>
+        <v>-0.0257</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8396</v>
+        <v>1.0498</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8396</v>
+        <v>1.0498</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8396</v>
+        <v>1.0498</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8396</v>
+        <v>1.0498</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8396</v>
+        <v>1.0498</v>
       </c>
       <c r="N17" t="n">
         <v>124</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7585</v>
+        <v>0.9107</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2676</v>
+        <v>0.3213</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1149</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7585</v>
+        <v>0.9107</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7585</v>
+        <v>0.6532</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.2575</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7585</v>
+        <v>0.6532</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7585</v>
+        <v>0.5294</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.2575</v>
       </c>
       <c r="K18" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7585</v>
+        <v>0.7868999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>111</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7227</v>
+        <v>0.7585</v>
       </c>
       <c r="C19" t="n">
-        <v>0.255</v>
+        <v>0.2676</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1294</v>
+        <v>-0.1417</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7227</v>
+        <v>0.7585</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7227</v>
+        <v>0.7585</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7227</v>
+        <v>0.7585</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7227</v>
+        <v>0.7585</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7227</v>
+        <v>0.7585</v>
       </c>
       <c r="N19" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5161</v>
+        <v>0.7231</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1821</v>
+        <v>0.2551</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2129</v>
+        <v>-0.1558</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5161</v>
+        <v>0.7231</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3979</v>
+        <v>0.6049</v>
       </c>
       <c r="G20" t="n">
         <v>0.1182</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3979</v>
+        <v>0.6049</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3225</v>
+        <v>0.4903</v>
       </c>
       <c r="J20" t="n">
         <v>0.1182</v>
@@ -1357,7 +1357,7 @@
         <v>78</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4407</v>
+        <v>0.6085</v>
       </c>
       <c r="N20" t="n">
         <v>208</v>
@@ -1366,78 +1366,78 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5102</v>
+        <v>0.6815</v>
       </c>
       <c r="C21" t="n">
-        <v>0.18</v>
+        <v>0.2405</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2153</v>
+        <v>-0.1724</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5102</v>
+        <v>0.6815</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5102</v>
+        <v>0.8102</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.1287</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5102</v>
+        <v>0.8102</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5102</v>
+        <v>0.6567</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.1287</v>
       </c>
       <c r="K21" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5102</v>
+        <v>0.5279999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>75</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3756</v>
+        <v>0.5365</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1325</v>
+        <v>0.1893</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2696</v>
+        <v>-0.2302</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3756</v>
+        <v>0.5365</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3756</v>
+        <v>0.5365</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3756</v>
+        <v>0.5365</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3756</v>
+        <v>0.5365</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3756</v>
+        <v>0.5365</v>
       </c>
       <c r="N22" t="n">
         <v>126</v>
@@ -1458,170 +1458,170 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3547</v>
+        <v>0.5102</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1252</v>
+        <v>0.18</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2781</v>
+        <v>-0.2406</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3547</v>
+        <v>0.5102</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3547</v>
+        <v>0.5102</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3547</v>
+        <v>0.5102</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3547</v>
+        <v>0.5102</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3547</v>
+        <v>0.5102</v>
       </c>
       <c r="N23" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3405</v>
+        <v>0.4243</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1201</v>
+        <v>0.1497</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2838</v>
+        <v>-0.2749</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3405</v>
+        <v>0.4243</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4692</v>
+        <v>0.4243</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1287</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4692</v>
+        <v>0.4243</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3803</v>
+        <v>0.4243</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1287</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="L24" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2516</v>
+        <v>0.4243</v>
       </c>
       <c r="N24" t="n">
-        <v>208</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3075</v>
+        <v>0.4184</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1085</v>
+        <v>0.1476</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2971</v>
+        <v>-0.2772</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3075</v>
+        <v>0.4184</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3075</v>
+        <v>0.4184</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3075</v>
+        <v>0.4184</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3075</v>
+        <v>0.4184</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3075</v>
+        <v>0.4184</v>
       </c>
       <c r="N25" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3025</v>
+        <v>0.3756</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1067</v>
+        <v>0.1325</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2992</v>
+        <v>-0.2943</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3025</v>
+        <v>0.3756</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3025</v>
+        <v>0.3756</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3025</v>
+        <v>0.3756</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3025</v>
+        <v>0.3756</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3025</v>
+        <v>0.3756</v>
       </c>
       <c r="N26" t="n">
         <v>126</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1224</v>
+        <v>0.3075</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0432</v>
+        <v>0.1085</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3719</v>
+        <v>-0.3214</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1224</v>
+        <v>0.3075</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1224</v>
+        <v>0.3075</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1224</v>
+        <v>0.3075</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1224</v>
+        <v>0.3075</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1224</v>
+        <v>0.3075</v>
       </c>
       <c r="N27" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>0.0213</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.397</v>
+        <v>-0.4199</v>
       </c>
       <c r="E28" t="n">
         <v>0.0603</v>
@@ -1744,7 +1744,7 @@
         <v>0.0155</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4037</v>
+        <v>-0.4265</v>
       </c>
       <c r="E29" t="n">
         <v>0.0438</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0492</v>
+        <v>0.003</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0174</v>
+        <v>0.0011</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4412</v>
+        <v>-0.4427</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0492</v>
+        <v>0.003</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5187</v>
+        <v>0.003</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4695</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5187</v>
+        <v>0.003</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4204</v>
+        <v>0.003</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4695</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="L30" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.04909999999999998</v>
+        <v>0.003</v>
       </c>
       <c r="N30" t="n">
-        <v>229</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.055</v>
+        <v>-0.0492</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0194</v>
+        <v>-0.0174</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4436</v>
+        <v>-0.4635</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.055</v>
+        <v>-0.0492</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.055</v>
+        <v>-0.5187</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.4695</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.055</v>
+        <v>-0.5187</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.055</v>
+        <v>-0.4204</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.4695</v>
       </c>
       <c r="K31" t="n">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.055</v>
+        <v>0.04909999999999998</v>
       </c>
       <c r="N31" t="n">
-        <v>124</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32">
@@ -1882,7 +1882,7 @@
         <v>-0.0893</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5236</v>
+        <v>-0.5447</v>
       </c>
       <c r="E32" t="n">
         <v>-0.2531</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1139</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5518</v>
+        <v>-0.5725</v>
       </c>
       <c r="E33" t="n">
         <v>-0.3228</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5425</v>
+        <v>-0.5094</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1914</v>
+        <v>-0.1797</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6405</v>
+        <v>-0.6469</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5425</v>
+        <v>-0.5094</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0916</v>
+        <v>0.1247</v>
       </c>
       <c r="G34" t="n">
         <v>-0.6341</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0916</v>
+        <v>0.1247</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0742</v>
+        <v>0.1011</v>
       </c>
       <c r="J34" t="n">
         <v>-0.6341</v>
@@ -2001,7 +2001,7 @@
         <v>104</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5599</v>
+        <v>-0.533</v>
       </c>
       <c r="N34" t="n">
         <v>205</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1965</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6463</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="E35" t="n">
         <v>-0.5569</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2605</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7196</v>
+        <v>-0.738</v>
       </c>
       <c r="E36" t="n">
         <v>-0.7382</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2607</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7198</v>
+        <v>-0.7382</v>
       </c>
       <c r="E37" t="n">
         <v>-0.7387</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4485</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9349</v>
+        <v>-0.9504</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2712</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4902</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9826</v>
+        <v>-0.9974</v>
       </c>
       <c r="E39" t="n">
         <v>-1.3893</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5484</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0493</v>
+        <v>-1.0631</v>
       </c>
       <c r="E40" t="n">
         <v>-1.5543</v>
@@ -2296,7 +2296,7 @@
         <v>-1.3847</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0067</v>
+        <v>-2.0074</v>
       </c>
       <c r="E41" t="n">
         <v>-3.9244</v>

--- a/database/event/2239/event_2239_evp_summary.xlsx
+++ b/database/event/2239/event_2239_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.656</v>
+        <v>6.5251</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7014</v>
+        <v>2.3024</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6062</v>
+        <v>2.3077</v>
       </c>
       <c r="E2" t="n">
-        <v>7.656</v>
+        <v>6.5251</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4617</v>
+        <v>2.9865</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1943</v>
+        <v>3.5386</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4617</v>
+        <v>5.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8058</v>
+        <v>2.6186</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1943</v>
+        <v>3.5386</v>
       </c>
       <c r="K2" t="n">
         <v>72</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>7.0001</v>
+        <v>6.1572</v>
       </c>
       <c r="N2" t="n">
         <v>229</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4209</v>
+        <v>5.7748</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9128</v>
+        <v>2.0377</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7158</v>
+        <v>1.969</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4209</v>
+        <v>5.7748</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4061</v>
+        <v>2.7641</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0148</v>
+        <v>3.0107</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4061</v>
+        <v>4.2527</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9502</v>
+        <v>2.2112</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0148</v>
+        <v>3.0107</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>4.965</v>
+        <v>5.2219</v>
       </c>
       <c r="N3" t="n">
         <v>308</v>
@@ -584,81 +584,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7559</v>
+        <v>4.7496</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6781</v>
+        <v>1.6759</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4508</v>
+        <v>1.5062</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7559</v>
+        <v>4.7496</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8208</v>
+        <v>2.6667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9351</v>
+        <v>2.0829</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8208</v>
+        <v>3.9096</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0969</v>
+        <v>2.0328</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9351</v>
+        <v>2.0829</v>
       </c>
       <c r="K4" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="L4" t="n">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="M4" t="n">
-        <v>4.032</v>
+        <v>4.1157</v>
       </c>
       <c r="N4" t="n">
-        <v>208</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5102</v>
+        <v>4.2779</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5914</v>
+        <v>1.5095</v>
       </c>
       <c r="D5" t="n">
-        <v>1.353</v>
+        <v>1.2932</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5102</v>
+        <v>4.2779</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6988</v>
+        <v>2.6089</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8114</v>
+        <v>1.669</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6988</v>
+        <v>3.7057</v>
       </c>
       <c r="I5" t="n">
-        <v>2.998</v>
+        <v>1.9268</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8114</v>
+        <v>1.669</v>
       </c>
       <c r="K5" t="n">
         <v>72</v>
@@ -667,7 +667,7 @@
         <v>157</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8094</v>
+        <v>3.5958</v>
       </c>
       <c r="N5" t="n">
         <v>229</v>
@@ -676,173 +676,173 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2979</v>
+        <v>4.1949</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5165</v>
+        <v>1.4802</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2684</v>
+        <v>1.2558</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2979</v>
+        <v>4.1949</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2003</v>
+        <v>3.2039</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0976</v>
+        <v>0.991</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2003</v>
+        <v>5.8022</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5939</v>
+        <v>3.0169</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0976</v>
+        <v>0.991</v>
       </c>
       <c r="K6" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="L6" t="n">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6915</v>
+        <v>4.0079</v>
       </c>
       <c r="N6" t="n">
-        <v>308</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2159</v>
+        <v>4.1568</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4876</v>
+        <v>1.4667</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2357</v>
+        <v>1.2386</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2159</v>
+        <v>4.1568</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9473</v>
+        <v>3.3757</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2686</v>
+        <v>0.7811</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9473</v>
+        <v>6.4077</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5783</v>
+        <v>3.3317</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2686</v>
+        <v>0.7811</v>
       </c>
       <c r="K7" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="L7" t="n">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8469</v>
+        <v>4.1128</v>
       </c>
       <c r="N7" t="n">
-        <v>308</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0905</v>
+        <v>4.0466</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4433</v>
+        <v>1.4279</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1857</v>
+        <v>1.1888</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0905</v>
+        <v>4.0466</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2104</v>
+        <v>2.8615</v>
       </c>
       <c r="G8" t="n">
-        <v>1.88</v>
+        <v>1.1851</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2104</v>
+        <v>4.5958</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7916</v>
+        <v>2.3896</v>
       </c>
       <c r="J8" t="n">
-        <v>1.88</v>
+        <v>1.1851</v>
       </c>
       <c r="K8" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="L8" t="n">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6716</v>
+        <v>3.5747</v>
       </c>
       <c r="N8" t="n">
-        <v>229</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5314</v>
+        <v>3.0029</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2461</v>
+        <v>1.0596</v>
       </c>
       <c r="D9" t="n">
-        <v>0.963</v>
+        <v>0.7176</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5314</v>
+        <v>3.0029</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2347</v>
+        <v>2.682</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7033</v>
+        <v>0.3209</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4767</v>
+        <v>3.9634</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6285</v>
+        <v>2.0608</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7033</v>
+        <v>0.3209</v>
       </c>
       <c r="K9" t="n">
         <v>101</v>
@@ -851,7 +851,7 @@
         <v>104</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9252</v>
+        <v>2.3817</v>
       </c>
       <c r="N9" t="n">
         <v>205</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5944</v>
+        <v>2.9407</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9154</v>
+        <v>1.0376</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5897</v>
+        <v>0.6896</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5944</v>
+        <v>2.9407</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4086</v>
+        <v>3.3511</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1858</v>
+        <v>-0.4104</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4086</v>
+        <v>6.3209</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9522</v>
+        <v>3.2866</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1858</v>
+        <v>-0.4104</v>
       </c>
       <c r="K10" t="n">
         <v>101</v>
@@ -897,7 +897,7 @@
         <v>104</v>
       </c>
       <c r="M10" t="n">
-        <v>2.138</v>
+        <v>2.8762</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2189</v>
+        <v>2.8784</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7829</v>
+        <v>1.0157</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4401</v>
+        <v>0.6614</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2189</v>
+        <v>2.8784</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8645</v>
+        <v>2.4741</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3544</v>
+        <v>0.4043</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8645</v>
+        <v>3.2309</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5112</v>
+        <v>1.6799</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3544</v>
+        <v>0.4043</v>
       </c>
       <c r="K11" t="n">
         <v>101</v>
@@ -943,7 +943,7 @@
         <v>104</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8656</v>
+        <v>2.0842</v>
       </c>
       <c r="N11" t="n">
         <v>205</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0873</v>
+        <v>2.555</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7365</v>
+        <v>0.9015</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3877</v>
+        <v>0.5154</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0873</v>
+        <v>2.555</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0873</v>
+        <v>1.3876</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.1674</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0873</v>
+        <v>1.3876</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0873</v>
+        <v>0.7215</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.1674</v>
       </c>
       <c r="K12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0873</v>
+        <v>1.8889</v>
       </c>
       <c r="N12" t="n">
-        <v>126</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0505</v>
+        <v>2.4046</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7235</v>
+        <v>0.8485</v>
       </c>
       <c r="D13" t="n">
-        <v>0.373</v>
+        <v>0.4475</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0505</v>
+        <v>2.4046</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0505</v>
+        <v>2.4046</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0505</v>
+        <v>2.4046</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0505</v>
+        <v>2.4046</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0505</v>
+        <v>2.4046</v>
       </c>
       <c r="N13" t="n">
         <v>124</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5859</v>
+        <v>2.3237</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5596</v>
+        <v>0.8199</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1879</v>
+        <v>0.411</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5859</v>
+        <v>2.3237</v>
       </c>
       <c r="F14" t="n">
-        <v>0.416</v>
+        <v>2.3237</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1699</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.416</v>
+        <v>2.3237</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3372</v>
+        <v>2.3237</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1699</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L14" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5071</v>
+        <v>2.3237</v>
       </c>
       <c r="N14" t="n">
-        <v>308</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4388</v>
+        <v>2.1044</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5077</v>
+        <v>0.7425</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1293</v>
+        <v>0.312</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4388</v>
+        <v>2.1044</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4388</v>
+        <v>1.8427</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.2617</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4388</v>
+        <v>1.8427</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4388</v>
+        <v>0.9581</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.2617</v>
       </c>
       <c r="K15" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4388</v>
+        <v>1.2198</v>
       </c>
       <c r="N15" t="n">
-        <v>126</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.229</v>
+        <v>1.9615</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4337</v>
+        <v>0.6921</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0457</v>
+        <v>0.2475</v>
       </c>
       <c r="E16" t="n">
-        <v>1.229</v>
+        <v>1.9615</v>
       </c>
       <c r="F16" t="n">
-        <v>1.229</v>
+        <v>1.9225</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="H16" t="n">
-        <v>1.229</v>
+        <v>1.9225</v>
       </c>
       <c r="I16" t="n">
-        <v>1.229</v>
+        <v>0.9996</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="K16" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M16" t="n">
-        <v>1.229</v>
+        <v>1.0386</v>
       </c>
       <c r="N16" t="n">
-        <v>111</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0498</v>
+        <v>1.7855</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3704</v>
+        <v>0.63</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0257</v>
+        <v>0.1681</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0498</v>
+        <v>1.7855</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0498</v>
+        <v>1.7855</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0498</v>
+        <v>1.7855</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0498</v>
+        <v>1.7855</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0498</v>
+        <v>1.7855</v>
       </c>
       <c r="N17" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9107</v>
+        <v>1.5405</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3213</v>
+        <v>0.5436</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08110000000000001</v>
+        <v>0.0574</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9107</v>
+        <v>1.5405</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6532</v>
+        <v>1.2213</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2575</v>
+        <v>0.3192</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6532</v>
+        <v>1.2213</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5294</v>
+        <v>0.635</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2575</v>
+        <v>0.3192</v>
       </c>
       <c r="K18" t="n">
         <v>130</v>
@@ -1265,7 +1265,7 @@
         <v>78</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7868999999999999</v>
+        <v>0.9541999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>208</v>
@@ -1274,32 +1274,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7585</v>
+        <v>1.3148</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2676</v>
+        <v>0.4639</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1417</v>
+        <v>-0.0444</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7585</v>
+        <v>1.3148</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585</v>
+        <v>1.3148</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7585</v>
+        <v>1.3148</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7585</v>
+        <v>1.3148</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7585</v>
+        <v>1.3148</v>
       </c>
       <c r="N19" t="n">
         <v>111</v>
@@ -1320,277 +1320,277 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7231</v>
+        <v>1.2006</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2551</v>
+        <v>0.4236</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1558</v>
+        <v>-0.096</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7231</v>
+        <v>1.2006</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6049</v>
+        <v>1.2006</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1182</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6049</v>
+        <v>1.2006</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4903</v>
+        <v>1.2006</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1182</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="L20" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6085</v>
+        <v>1.2006</v>
       </c>
       <c r="N20" t="n">
-        <v>208</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6815</v>
+        <v>1.0499</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2405</v>
+        <v>0.3705</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1724</v>
+        <v>-0.164</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6815</v>
+        <v>1.0499</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8102</v>
+        <v>1.0499</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1287</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8102</v>
+        <v>1.0499</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6567</v>
+        <v>1.0499</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1287</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L21" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5279999999999999</v>
+        <v>1.0499</v>
       </c>
       <c r="N21" t="n">
-        <v>208</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5365</v>
+        <v>1.0449</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1893</v>
+        <v>0.3687</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2302</v>
+        <v>-0.1663</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5365</v>
+        <v>1.0449</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5365</v>
+        <v>1.0449</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5365</v>
+        <v>1.0449</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5365</v>
+        <v>1.0449</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5365</v>
+        <v>1.0449</v>
       </c>
       <c r="N22" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5102</v>
+        <v>0.9282</v>
       </c>
       <c r="C23" t="n">
-        <v>0.18</v>
+        <v>0.3275</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2406</v>
+        <v>-0.219</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5102</v>
+        <v>0.9282</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5102</v>
+        <v>0.9282</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5102</v>
+        <v>0.9282</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5102</v>
+        <v>0.9282</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5102</v>
+        <v>0.9282</v>
       </c>
       <c r="N23" t="n">
-        <v>75</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4243</v>
+        <v>0.8394</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1497</v>
+        <v>0.2962</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2749</v>
+        <v>-0.2591</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4243</v>
+        <v>0.8394</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4243</v>
+        <v>0.8394</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4243</v>
+        <v>0.8394</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4243</v>
+        <v>0.8394</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4243</v>
+        <v>0.8394</v>
       </c>
       <c r="N24" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4184</v>
+        <v>0.759</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1476</v>
+        <v>0.2678</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2772</v>
+        <v>-0.2954</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4184</v>
+        <v>0.759</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4184</v>
+        <v>2.1995</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-1.4405</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4184</v>
+        <v>2.2633</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4184</v>
+        <v>1.1768</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-1.4405</v>
       </c>
       <c r="K25" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4184</v>
+        <v>-0.2636999999999998</v>
       </c>
       <c r="N25" t="n">
-        <v>126</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3756</v>
+        <v>0.7272</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1325</v>
+        <v>0.2566</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2943</v>
+        <v>-0.3097</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3756</v>
+        <v>0.7272</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3756</v>
+        <v>0.7272</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3756</v>
+        <v>0.7272</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3756</v>
+        <v>0.7272</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3756</v>
+        <v>0.7272</v>
       </c>
       <c r="N26" t="n">
         <v>126</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3075</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1085</v>
+        <v>0.2527</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3214</v>
+        <v>-0.3147</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3075</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3075</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3075</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3075</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3075</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>111</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0603</v>
+        <v>0.5495</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0213</v>
+        <v>0.1939</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4199</v>
+        <v>-0.3899</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0603</v>
+        <v>0.5495</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0603</v>
+        <v>-0.3698</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.9193</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0603</v>
+        <v>-0.3698</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0603</v>
+        <v>-0.1923</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.9193</v>
       </c>
       <c r="K28" t="n">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0603</v>
+        <v>0.727</v>
       </c>
       <c r="N28" t="n">
-        <v>111</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0438</v>
+        <v>0.5163</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0155</v>
+        <v>0.1822</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4265</v>
+        <v>-0.4049</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0438</v>
+        <v>0.5163</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0438</v>
+        <v>0.5163</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0438</v>
+        <v>0.5163</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0438</v>
+        <v>0.5163</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0438</v>
+        <v>0.5163</v>
       </c>
       <c r="N29" t="n">
-        <v>75</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.003</v>
+        <v>0.4409</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0011</v>
+        <v>0.1556</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4427</v>
+        <v>-0.439</v>
       </c>
       <c r="E30" t="n">
-        <v>0.003</v>
+        <v>0.4409</v>
       </c>
       <c r="F30" t="n">
-        <v>0.003</v>
+        <v>0.4409</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.003</v>
+        <v>0.4409</v>
       </c>
       <c r="I30" t="n">
-        <v>0.003</v>
+        <v>0.4409</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.003</v>
+        <v>0.4409</v>
       </c>
       <c r="N30" t="n">
         <v>124</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0492</v>
+        <v>0.3589</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0174</v>
+        <v>0.1266</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4635</v>
+        <v>-0.476</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0492</v>
+        <v>0.3589</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5187</v>
+        <v>0.3179</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4695</v>
+        <v>0.041</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5187</v>
+        <v>0.3179</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4204</v>
+        <v>0.1653</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4695</v>
+        <v>0.041</v>
       </c>
       <c r="K31" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="L31" t="n">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="M31" t="n">
-        <v>0.04909999999999998</v>
+        <v>0.2063</v>
       </c>
       <c r="N31" t="n">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2531</v>
+        <v>0.1898</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0893</v>
+        <v>0.067</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5447</v>
+        <v>-0.5523</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2531</v>
+        <v>0.1898</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1194</v>
+        <v>0.1898</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1337</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1194</v>
+        <v>0.1898</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0968</v>
+        <v>0.1898</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.1337</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="L32" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2305</v>
+        <v>0.1898</v>
       </c>
       <c r="N32" t="n">
-        <v>208</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3228</v>
+        <v>0.1802</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1139</v>
+        <v>0.0636</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5725</v>
+        <v>-0.5567</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3228</v>
+        <v>0.1802</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3228</v>
+        <v>0.1802</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3228</v>
+        <v>0.1802</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3228</v>
+        <v>0.1802</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3228</v>
+        <v>0.1802</v>
       </c>
       <c r="N33" t="n">
         <v>124</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5094</v>
+        <v>0.1535</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1797</v>
+        <v>0.0542</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6469</v>
+        <v>-0.5687</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5094</v>
+        <v>0.1535</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1247</v>
+        <v>0.1535</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6341</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1247</v>
+        <v>0.1535</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1011</v>
+        <v>0.1535</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6341</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="L34" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.533</v>
+        <v>0.1535</v>
       </c>
       <c r="N34" t="n">
-        <v>205</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5569</v>
+        <v>0.1092</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1965</v>
+        <v>0.0385</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.5887</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5569</v>
+        <v>0.1092</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5569</v>
+        <v>0.5024</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.3932</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5569</v>
+        <v>0.5024</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5569</v>
+        <v>0.2612</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.3932</v>
       </c>
       <c r="K35" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5569</v>
+        <v>-0.132</v>
       </c>
       <c r="N35" t="n">
-        <v>75</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7382</v>
+        <v>-0.3492</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2605</v>
+        <v>-0.1232</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.738</v>
+        <v>-0.7957</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7382</v>
+        <v>-0.3492</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7382</v>
+        <v>-0.3492</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7382</v>
+        <v>-0.3492</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7382</v>
+        <v>-0.3492</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7382</v>
+        <v>-0.3492</v>
       </c>
       <c r="N36" t="n">
         <v>111</v>
@@ -2102,124 +2102,124 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7387</v>
+        <v>-0.3925</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2607</v>
+        <v>-0.1385</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7382</v>
+        <v>-0.8152</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7387</v>
+        <v>-0.3925</v>
       </c>
       <c r="F37" t="n">
-        <v>1.179</v>
+        <v>-0.3925</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.9177</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.179</v>
+        <v>-0.3925</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9556</v>
+        <v>-0.3925</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.9177</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L37" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9621</v>
+        <v>-0.3925</v>
       </c>
       <c r="N37" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2712</v>
+        <v>-0.905</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4485</v>
+        <v>-0.3193</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9504</v>
+        <v>-1.0466</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2712</v>
+        <v>-0.905</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7904</v>
+        <v>-0.905</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5192</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7904</v>
+        <v>-0.905</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4512</v>
+        <v>-0.905</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5192</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="L38" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.905</v>
       </c>
       <c r="N38" t="n">
-        <v>308</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3893</v>
+        <v>-1.0205</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4902</v>
+        <v>-0.3601</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9974</v>
+        <v>-1.0987</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3893</v>
+        <v>-1.0205</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3893</v>
+        <v>-1.0205</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3893</v>
+        <v>-1.0205</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3893</v>
+        <v>-1.0205</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3893</v>
+        <v>-1.0205</v>
       </c>
       <c r="N39" t="n">
         <v>75</v>
@@ -2240,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5543</v>
+        <v>-1.1511</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5484</v>
+        <v>-0.4062</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0631</v>
+        <v>-1.1577</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5543</v>
+        <v>-1.1511</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5543</v>
+        <v>-1.8992</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.7481</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5543</v>
+        <v>-1.8992</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5543</v>
+        <v>-0.9875</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.7481</v>
       </c>
       <c r="K40" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5543</v>
+        <v>-0.2394000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>75</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.9244</v>
+        <v>-5.38</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.3847</v>
+        <v>-1.8984</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0074</v>
+        <v>-3.0668</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.9244</v>
+        <v>-5.38</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.0678</v>
+        <v>-5.6588</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1434</v>
+        <v>0.2788</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.0678</v>
+        <v>-5.6588</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.2971</v>
+        <v>-2.9423</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1434</v>
+        <v>0.2788</v>
       </c>
       <c r="K41" t="n">
         <v>101</v>
@@ -2323,7 +2323,7 @@
         <v>104</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.1537</v>
+        <v>-2.6635</v>
       </c>
       <c r="N41" t="n">
         <v>205</v>
@@ -2429,10 +2429,10 @@
         <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0747</v>
+        <v>0.0246</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4193</v>
+        <v>0.4674</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.78</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2533</v>
+        <v>-0.2132</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.8127</v>
+        <v>-4.0508</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2849</v>
+        <v>-0.2339</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.4131</v>
+        <v>-4.4441</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.49</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7155</v>
+        <v>-0.4865</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.5945</v>
+        <v>-9.243499999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.33</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9161</v>
+        <v>-0.6369</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.4059</v>
+        <v>-12.1011</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.34</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4287</v>
+        <v>1.211</v>
       </c>
       <c r="J7" t="n">
-        <v>27.1453</v>
+        <v>23.009</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.95</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0714</v>
+        <v>0.9915</v>
       </c>
       <c r="J8" t="n">
-        <v>20.3566</v>
+        <v>18.8385</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.47</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5332</v>
+        <v>0.5434</v>
       </c>
       <c r="J9" t="n">
-        <v>10.1308</v>
+        <v>10.3246</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3442</v>
+        <v>0.37</v>
       </c>
       <c r="J10" t="n">
-        <v>6.5398</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.03</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0527</v>
+        <v>-0.0016</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0013</v>
+        <v>-0.0304</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.74</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6029</v>
+        <v>1.3978</v>
       </c>
       <c r="J12" t="n">
-        <v>38.4696</v>
+        <v>33.5472</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.56</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2649</v>
+        <v>1.1828</v>
       </c>
       <c r="J13" t="n">
-        <v>30.3576</v>
+        <v>28.3872</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.32</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7176</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>17.2224</v>
+        <v>19.392</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.09</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1473</v>
+        <v>0.2367</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5352</v>
+        <v>5.6808</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1473</v>
+        <v>0.2367</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5352</v>
+        <v>5.6808</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.41</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7377</v>
+        <v>0.9315</v>
       </c>
       <c r="J17" t="n">
-        <v>17.7048</v>
+        <v>22.356</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.74</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4059</v>
+        <v>-0.2714</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.7416</v>
+        <v>-6.5136</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.67</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.51</v>
+        <v>-0.3378</v>
       </c>
       <c r="J19" t="n">
-        <v>-12.24</v>
+        <v>-8.107200000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.64</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5518</v>
+        <v>-0.3661</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.2432</v>
+        <v>-8.7864</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.733</v>
+        <v>-0.4963</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.592</v>
+        <v>-11.9112</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.37</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0191</v>
+        <v>0.9935</v>
       </c>
       <c r="J22" t="n">
-        <v>36.6876</v>
+        <v>35.766</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5457</v>
+        <v>0.5154</v>
       </c>
       <c r="J23" t="n">
-        <v>19.6452</v>
+        <v>18.5544</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1681</v>
+        <v>-0.1113</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.0516</v>
+        <v>-4.0068</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2432</v>
+        <v>-0.1833</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.7552</v>
+        <v>-6.5988</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4872</v>
+        <v>-0.4266</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.5392</v>
+        <v>-15.3576</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4672</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>16.8192</v>
+        <v>19.8324</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2118</v>
+        <v>0.2374</v>
       </c>
       <c r="J28" t="n">
-        <v>7.6248</v>
+        <v>8.5464</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0376</v>
+        <v>0.0612</v>
       </c>
       <c r="J29" t="n">
-        <v>1.3536</v>
+        <v>2.2032</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2227</v>
+        <v>-0.1274</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.017200000000001</v>
+        <v>-4.5864</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2396</v>
+        <v>-0.1387</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.6256</v>
+        <v>-4.9932</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.44</v>
       </c>
       <c r="I32" t="n">
-        <v>0.657</v>
+        <v>0.4763</v>
       </c>
       <c r="J32" t="n">
-        <v>22.995</v>
+        <v>16.6705</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2472</v>
+        <v>0.2142</v>
       </c>
       <c r="J33" t="n">
-        <v>8.651999999999999</v>
+        <v>7.497</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1292</v>
+        <v>0.1329</v>
       </c>
       <c r="J34" t="n">
-        <v>4.522</v>
+        <v>4.6515</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0505</v>
+        <v>-0.0104</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.7675</v>
+        <v>-0.364</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.92</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2245</v>
+        <v>-0.1241</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.8575</v>
+        <v>-4.3435</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2816</v>
+        <v>0.2428</v>
       </c>
       <c r="J37" t="n">
-        <v>9.856</v>
+        <v>8.497999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1975</v>
+        <v>0.1674</v>
       </c>
       <c r="J38" t="n">
-        <v>6.9125</v>
+        <v>5.859</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0149</v>
+        <v>0.026</v>
       </c>
       <c r="J39" t="n">
-        <v>0.5215</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0149</v>
+        <v>0.026</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5215</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.91</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2204</v>
+        <v>-0.1266</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.714</v>
+        <v>-4.431</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4659</v>
+        <v>0.4586</v>
       </c>
       <c r="J42" t="n">
-        <v>21.4314</v>
+        <v>21.0956</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1336</v>
+        <v>0.1385</v>
       </c>
       <c r="J43" t="n">
-        <v>6.1456</v>
+        <v>6.371</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0941</v>
+        <v>-0.0504</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.3286</v>
+        <v>-2.3184</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1568</v>
+        <v>-0.0885</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.2128</v>
+        <v>-4.071</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3845</v>
+        <v>-0.2395</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.687</v>
+        <v>-11.017</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6574</v>
+        <v>0.5101</v>
       </c>
       <c r="J47" t="n">
-        <v>30.2404</v>
+        <v>23.4646</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5542</v>
+        <v>0.451</v>
       </c>
       <c r="J48" t="n">
-        <v>25.4932</v>
+        <v>20.746</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.272</v>
+        <v>0.2958</v>
       </c>
       <c r="J49" t="n">
-        <v>12.512</v>
+        <v>13.6068</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.09</v>
       </c>
       <c r="I50" t="n">
-        <v>0.272</v>
+        <v>0.2958</v>
       </c>
       <c r="J50" t="n">
-        <v>12.512</v>
+        <v>13.6068</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.92</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3843</v>
+        <v>-0.3181</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.6778</v>
+        <v>-14.6326</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.19</v>
       </c>
       <c r="I52" t="n">
-        <v>0.462</v>
+        <v>0.4533</v>
       </c>
       <c r="J52" t="n">
-        <v>10.626</v>
+        <v>10.4259</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2713</v>
+        <v>0.2762</v>
       </c>
       <c r="J53" t="n">
-        <v>6.2399</v>
+        <v>6.3526</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.65</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.5273</v>
+        <v>-0.3519</v>
       </c>
       <c r="J54" t="n">
-        <v>-12.1279</v>
+        <v>-8.0937</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.54</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6757</v>
+        <v>-0.4548</v>
       </c>
       <c r="J55" t="n">
-        <v>-15.5411</v>
+        <v>-10.4604</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.35</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.9066</v>
+        <v>-0.63</v>
       </c>
       <c r="J56" t="n">
-        <v>-20.8518</v>
+        <v>-14.49</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.67</v>
       </c>
       <c r="I57" t="n">
-        <v>1.4609</v>
+        <v>1.0349</v>
       </c>
       <c r="J57" t="n">
-        <v>33.6007</v>
+        <v>23.8027</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.5</v>
       </c>
       <c r="I58" t="n">
-        <v>1.1283</v>
+        <v>0.8314</v>
       </c>
       <c r="J58" t="n">
-        <v>25.9509</v>
+        <v>19.1222</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.31</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6767</v>
+        <v>0.5967</v>
       </c>
       <c r="J59" t="n">
-        <v>15.5641</v>
+        <v>13.7241</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.25</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5376</v>
+        <v>0.5157</v>
       </c>
       <c r="J60" t="n">
-        <v>12.3648</v>
+        <v>11.8611</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.23</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4907</v>
+        <v>0.4877</v>
       </c>
       <c r="J61" t="n">
-        <v>11.2861</v>
+        <v>11.2171</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3913</v>
+        <v>0.3308</v>
       </c>
       <c r="J62" t="n">
-        <v>8.9999</v>
+        <v>7.6084</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>0.051</v>
+        <v>0.0058</v>
       </c>
       <c r="J63" t="n">
-        <v>1.173</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.73</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4336</v>
+        <v>-0.285</v>
       </c>
       <c r="J64" t="n">
-        <v>-9.972799999999999</v>
+        <v>-6.555</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5194</v>
+        <v>-0.3421</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.9462</v>
+        <v>-7.8683</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6643</v>
+        <v>-0.445</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.2789</v>
+        <v>-10.235</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.81</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0073</v>
+        <v>0.6825</v>
       </c>
       <c r="J67" t="n">
-        <v>23.1679</v>
+        <v>15.6975</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3479</v>
+        <v>0.3381</v>
       </c>
       <c r="J68" t="n">
-        <v>8.0017</v>
+        <v>7.7763</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.25</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3334</v>
+        <v>0.3292</v>
       </c>
       <c r="J69" t="n">
-        <v>7.6682</v>
+        <v>7.5716</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.16</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2033</v>
+        <v>0.2215</v>
       </c>
       <c r="J70" t="n">
-        <v>4.6759</v>
+        <v>5.0945</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0118</v>
+        <v>0.0301</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.2714</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2.04</v>
       </c>
       <c r="I72" t="n">
-        <v>1.9726</v>
+        <v>1.5183</v>
       </c>
       <c r="J72" t="n">
-        <v>57.2054</v>
+        <v>44.0307</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5062</v>
       </c>
       <c r="J73" t="n">
-        <v>17.2028</v>
+        <v>14.6798</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.08</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1658</v>
+        <v>0.2386</v>
       </c>
       <c r="J74" t="n">
-        <v>4.8082</v>
+        <v>6.9194</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3681</v>
+        <v>-0.2891</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.6749</v>
+        <v>-8.383900000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.84</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.5763</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.5484</v>
+        <v>-16.7127</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.19</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3754</v>
+        <v>0.3883</v>
       </c>
       <c r="J77" t="n">
-        <v>10.8866</v>
+        <v>11.2607</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3459</v>
+        <v>0.3662</v>
       </c>
       <c r="J78" t="n">
-        <v>10.0311</v>
+        <v>10.6198</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.91</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2043</v>
+        <v>-0.1211</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.9247</v>
+        <v>-3.5119</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2219</v>
+        <v>-0.1323</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.4351</v>
+        <v>-3.8367</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4635</v>
+        <v>-0.2959</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.4415</v>
+        <v>-8.581099999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.62</v>
       </c>
       <c r="I82" t="n">
-        <v>1.46</v>
+        <v>1.0224</v>
       </c>
       <c r="J82" t="n">
-        <v>37.96</v>
+        <v>26.5824</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.14</v>
       </c>
       <c r="I83" t="n">
-        <v>0.356</v>
+        <v>0.3807</v>
       </c>
       <c r="J83" t="n">
-        <v>9.256</v>
+        <v>9.898199999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2413</v>
+        <v>0.3047</v>
       </c>
       <c r="J84" t="n">
-        <v>6.2738</v>
+        <v>7.9222</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.1</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2413</v>
+        <v>0.3047</v>
       </c>
       <c r="J85" t="n">
-        <v>6.2738</v>
+        <v>7.9222</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1781</v>
+        <v>-0.101</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.6306</v>
+        <v>-2.626</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.03</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1315</v>
+        <v>0.1134</v>
       </c>
       <c r="J87" t="n">
-        <v>3.419</v>
+        <v>2.9484</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.03</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1315</v>
+        <v>0.1134</v>
       </c>
       <c r="J88" t="n">
-        <v>3.419</v>
+        <v>2.9484</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.87</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2454</v>
+        <v>-0.1567</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.3804</v>
+        <v>-4.0742</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2628</v>
+        <v>-0.1671</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.8328</v>
+        <v>-4.3446</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.76</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4181</v>
+        <v>-0.2676</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.8706</v>
+        <v>-6.9576</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.51</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7225</v>
+        <v>0.9003</v>
       </c>
       <c r="J92" t="n">
-        <v>21.675</v>
+        <v>27.009</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.32</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4915</v>
+        <v>0.5994</v>
       </c>
       <c r="J93" t="n">
-        <v>14.745</v>
+        <v>17.982</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1277</v>
+        <v>0.1985</v>
       </c>
       <c r="J94" t="n">
-        <v>3.831</v>
+        <v>5.955</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0556</v>
+        <v>0.1128</v>
       </c>
       <c r="J95" t="n">
-        <v>1.668</v>
+        <v>3.384</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2997</v>
+        <v>-0.1743</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.991</v>
+        <v>-5.229</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.47</v>
       </c>
       <c r="I97" t="n">
-        <v>1.257</v>
+        <v>1.1572</v>
       </c>
       <c r="J97" t="n">
-        <v>37.71</v>
+        <v>34.716</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.96</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2134</v>
+        <v>-0.1694</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.402</v>
+        <v>-5.082</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.95</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2488</v>
+        <v>-0.2025</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.464</v>
+        <v>-6.075</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4646</v>
+        <v>-0.4116</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.938</v>
+        <v>-12.348</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.84</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5732</v>
+        <v>-0.5214</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.196</v>
+        <v>-15.642</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.78</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0807</v>
+        <v>1.2506</v>
       </c>
       <c r="J102" t="n">
-        <v>30.2596</v>
+        <v>35.0168</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.03</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1099</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>3.0772</v>
+        <v>2.7888</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2321</v>
+        <v>-0.141</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.4988</v>
+        <v>-3.948</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4728</v>
+        <v>-0.3032</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.2384</v>
+        <v>-8.489599999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.38</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8946</v>
+        <v>-0.622</v>
       </c>
       <c r="J106" t="n">
-        <v>-25.0488</v>
+        <v>-17.416</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.59</v>
       </c>
       <c r="I107" t="n">
-        <v>1.42</v>
+        <v>1.2685</v>
       </c>
       <c r="J107" t="n">
-        <v>39.76</v>
+        <v>35.518</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="J108" t="n">
-        <v>20.2244</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4844</v>
+        <v>0.4942</v>
       </c>
       <c r="J109" t="n">
-        <v>13.5632</v>
+        <v>13.8376</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0469</v>
+        <v>0.0175</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.3132</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.75</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.835</v>
+        <v>-0.7914</v>
       </c>
       <c r="J111" t="n">
-        <v>-23.38</v>
+        <v>-22.1592</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.68</v>
       </c>
       <c r="I112" t="n">
-        <v>1.5256</v>
+        <v>1.3434</v>
       </c>
       <c r="J112" t="n">
-        <v>36.6144</v>
+        <v>32.2416</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.42</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0128</v>
+        <v>1.0172</v>
       </c>
       <c r="J113" t="n">
-        <v>24.3072</v>
+        <v>24.4128</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.3</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7325</v>
+        <v>0.7743</v>
       </c>
       <c r="J114" t="n">
-        <v>17.58</v>
+        <v>18.5832</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.18</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4111</v>
+        <v>0.4945</v>
       </c>
       <c r="J115" t="n">
-        <v>9.866400000000001</v>
+        <v>11.868</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.86</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.5365</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.5032</v>
+        <v>-12.876</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.32</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6276</v>
+        <v>0.7711</v>
       </c>
       <c r="J117" t="n">
-        <v>15.0624</v>
+        <v>18.5064</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.98</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0414</v>
+        <v>-0.0042</v>
       </c>
       <c r="J118" t="n">
-        <v>0.9936</v>
+        <v>-0.1008</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.58</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.6303</v>
+        <v>-0.4213</v>
       </c>
       <c r="J119" t="n">
-        <v>-15.1272</v>
+        <v>-10.1112</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.669</v>
+        <v>-0.4493</v>
       </c>
       <c r="J120" t="n">
-        <v>-16.056</v>
+        <v>-10.7832</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.5</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7318</v>
+        <v>-0.4955</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.5632</v>
+        <v>-11.892</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6343</v>
+        <v>0.7719</v>
       </c>
       <c r="J122" t="n">
-        <v>19.029</v>
+        <v>23.157</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.06</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1561</v>
+        <v>0.1622</v>
       </c>
       <c r="J123" t="n">
-        <v>4.683</v>
+        <v>4.866</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.89</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2442</v>
+        <v>-0.145</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.326</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.84</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3239</v>
+        <v>-0.1981</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.717000000000001</v>
+        <v>-5.943</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3686</v>
+        <v>-0.2287</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.058</v>
+        <v>-6.861</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.37</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9941</v>
+        <v>0.9766</v>
       </c>
       <c r="J127" t="n">
-        <v>29.823</v>
+        <v>29.298</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.621</v>
+        <v>0.6026</v>
       </c>
       <c r="J128" t="n">
-        <v>18.63</v>
+        <v>18.078</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.19</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5689</v>
+        <v>0.5528</v>
       </c>
       <c r="J129" t="n">
-        <v>17.067</v>
+        <v>16.584</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0139</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>0.417</v>
+        <v>2.043</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.8</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.708</v>
+        <v>-0.6546</v>
       </c>
       <c r="J131" t="n">
-        <v>-21.24</v>
+        <v>-19.638</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.37</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6024</v>
+        <v>0.729</v>
       </c>
       <c r="J132" t="n">
-        <v>16.8672</v>
+        <v>20.412</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.22</v>
+        <v>0.2416</v>
       </c>
       <c r="J133" t="n">
-        <v>6.16</v>
+        <v>6.7648</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.05</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1259</v>
+        <v>0.1356</v>
       </c>
       <c r="J134" t="n">
-        <v>3.5252</v>
+        <v>3.7968</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.96</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1226</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.4328</v>
+        <v>-1.8256</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.62</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6243</v>
+        <v>-0.413</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.4804</v>
+        <v>-11.564</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.31</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8489</v>
+        <v>0.8357</v>
       </c>
       <c r="J137" t="n">
-        <v>23.7692</v>
+        <v>23.3996</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4983</v>
+        <v>0.4973</v>
       </c>
       <c r="J138" t="n">
-        <v>13.9524</v>
+        <v>13.9244</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2709</v>
+        <v>0.316</v>
       </c>
       <c r="J139" t="n">
-        <v>7.5852</v>
+        <v>8.848000000000001</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2088</v>
+        <v>0.259</v>
       </c>
       <c r="J140" t="n">
-        <v>5.8464</v>
+        <v>7.252</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.04</v>
       </c>
       <c r="I141" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.1342</v>
       </c>
       <c r="J141" t="n">
-        <v>2.1644</v>
+        <v>3.7576</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.83</v>
       </c>
       <c r="I142" t="n">
-        <v>1.7444</v>
+        <v>1.4932</v>
       </c>
       <c r="J142" t="n">
-        <v>38.3768</v>
+        <v>32.8504</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.37</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8114</v>
+        <v>0.9085</v>
       </c>
       <c r="J143" t="n">
-        <v>17.8508</v>
+        <v>19.987</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.36</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7877</v>
+        <v>0.8875</v>
       </c>
       <c r="J144" t="n">
-        <v>17.3294</v>
+        <v>19.525</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.24</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5104</v>
+        <v>0.6166</v>
       </c>
       <c r="J145" t="n">
-        <v>11.2288</v>
+        <v>13.5652</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.21</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4397</v>
+        <v>0.5442</v>
       </c>
       <c r="J146" t="n">
-        <v>9.673400000000001</v>
+        <v>11.9724</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.86</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.134</v>
+        <v>-0.1303</v>
       </c>
       <c r="J147" t="n">
-        <v>-2.948</v>
+        <v>-2.8666</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.75</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3109</v>
+        <v>-0.2479</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.8398</v>
+        <v>-5.4538</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3271</v>
+        <v>-0.2578</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.1962</v>
+        <v>-5.6716</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5697</v>
+        <v>-0.3866</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.5334</v>
+        <v>-8.5052</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.47</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7466</v>
+        <v>-0.5082</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.4252</v>
+        <v>-11.1804</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.16</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3388</v>
+        <v>0.3767</v>
       </c>
       <c r="J152" t="n">
-        <v>8.470000000000001</v>
+        <v>9.4175</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.04</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1322</v>
+        <v>0.1248</v>
       </c>
       <c r="J153" t="n">
-        <v>3.305</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1372</v>
+        <v>-0.0843</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.43</v>
+        <v>-2.1075</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.93</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1576</v>
+        <v>-0.096</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.94</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.73</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4724</v>
+        <v>-0.3029</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.81</v>
+        <v>-7.5725</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.27</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7786</v>
+        <v>0.7552</v>
       </c>
       <c r="J157" t="n">
-        <v>19.465</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.15</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4718</v>
+        <v>0.4555</v>
       </c>
       <c r="J158" t="n">
-        <v>11.795</v>
+        <v>11.3875</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4133</v>
+        <v>0.403</v>
       </c>
       <c r="J159" t="n">
-        <v>10.3325</v>
+        <v>10.075</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0229</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.9925</v>
+        <v>-0.5725</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.95</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2905</v>
+        <v>-0.2242</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.2625</v>
+        <v>-5.605</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2394</v>
+        <v>1.1639</v>
       </c>
       <c r="J162" t="n">
-        <v>28.5062</v>
+        <v>26.7697</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.4</v>
       </c>
       <c r="I163" t="n">
-        <v>0.946</v>
+        <v>0.976</v>
       </c>
       <c r="J163" t="n">
-        <v>21.758</v>
+        <v>22.448</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.34</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8018</v>
+        <v>0.8548</v>
       </c>
       <c r="J164" t="n">
-        <v>18.4414</v>
+        <v>19.6604</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.26</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5893</v>
+        <v>0.6783</v>
       </c>
       <c r="J165" t="n">
-        <v>13.5539</v>
+        <v>15.6009</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.11</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2118</v>
+        <v>0.3003</v>
       </c>
       <c r="J166" t="n">
-        <v>4.8714</v>
+        <v>6.9069</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.13</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3285</v>
+        <v>0.3546</v>
       </c>
       <c r="J167" t="n">
-        <v>7.5555</v>
+        <v>8.155799999999999</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3126</v>
+        <v>0.3339</v>
       </c>
       <c r="J168" t="n">
-        <v>7.1898</v>
+        <v>7.6797</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.72</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4619</v>
+        <v>-0.3003</v>
       </c>
       <c r="J169" t="n">
-        <v>-10.6237</v>
+        <v>-6.9069</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4899</v>
+        <v>-0.3194</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.2677</v>
+        <v>-7.3462</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.65</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5575</v>
+        <v>-0.3668</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.8225</v>
+        <v>-8.436400000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.07</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2626</v>
+        <v>0.2649</v>
       </c>
       <c r="J172" t="n">
-        <v>6.3024</v>
+        <v>6.3576</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.92</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0762</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>-1.8288</v>
+        <v>-2.0064</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4769</v>
+        <v>-0.3171</v>
       </c>
       <c r="J174" t="n">
-        <v>-11.4456</v>
+        <v>-7.6104</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.61</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.589</v>
+        <v>-0.3924</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.136</v>
+        <v>-9.4176</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.61</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.589</v>
+        <v>-0.3924</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.136</v>
+        <v>-9.4176</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.53</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2385</v>
+        <v>1.1593</v>
       </c>
       <c r="J177" t="n">
-        <v>29.724</v>
+        <v>27.8232</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.4</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9684</v>
+        <v>0.9838</v>
       </c>
       <c r="J178" t="n">
-        <v>23.2416</v>
+        <v>23.6112</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.3</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7306</v>
+        <v>0.774</v>
       </c>
       <c r="J179" t="n">
-        <v>17.5344</v>
+        <v>18.576</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6988</v>
+        <v>0.7524</v>
       </c>
       <c r="J180" t="n">
-        <v>16.7712</v>
+        <v>18.0576</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4159</v>
+        <v>-0.3356</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.9816</v>
+        <v>-8.054399999999999</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.57</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4042</v>
+        <v>1.257</v>
       </c>
       <c r="J182" t="n">
-        <v>40.7218</v>
+        <v>36.453</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.3</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8416</v>
+        <v>0.8224</v>
       </c>
       <c r="J183" t="n">
-        <v>24.4064</v>
+        <v>23.8496</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4028</v>
+        <v>0.4006</v>
       </c>
       <c r="J184" t="n">
-        <v>11.6812</v>
+        <v>11.6174</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.78</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.754</v>
+        <v>-0.7045</v>
       </c>
       <c r="J185" t="n">
-        <v>-21.866</v>
+        <v>-20.4305</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.754</v>
+        <v>-0.7045</v>
       </c>
       <c r="J186" t="n">
-        <v>-21.866</v>
+        <v>-20.4305</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3885</v>
+        <v>0.4433</v>
       </c>
       <c r="J187" t="n">
-        <v>11.2665</v>
+        <v>12.8557</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.07</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1801</v>
+        <v>0.1868</v>
       </c>
       <c r="J188" t="n">
-        <v>5.2229</v>
+        <v>5.4172</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.04</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1209</v>
+        <v>0.1189</v>
       </c>
       <c r="J189" t="n">
-        <v>3.5061</v>
+        <v>3.4481</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0262</v>
+        <v>-0.0198</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.7598</v>
+        <v>-0.5742</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6069</v>
+        <v>-0.4002</v>
       </c>
       <c r="J191" t="n">
-        <v>-17.6001</v>
+        <v>-11.6058</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.08</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2395</v>
+        <v>0.2416</v>
       </c>
       <c r="J192" t="n">
-        <v>5.9875</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.93</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1037</v>
+        <v>-0.0887</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.5925</v>
+        <v>-2.2175</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1231</v>
+        <v>-0.1004</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.0775</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.8</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3486</v>
+        <v>-0.2244</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.715</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.67</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.37</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0709</v>
+        <v>1.0469</v>
       </c>
       <c r="J197" t="n">
-        <v>26.7725</v>
+        <v>26.1725</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.42</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0498</v>
+        <v>1.0326</v>
       </c>
       <c r="J198" t="n">
-        <v>26.245</v>
+        <v>25.815</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.31</v>
       </c>
       <c r="I199" t="n">
-        <v>0.8061</v>
+        <v>0.8121</v>
       </c>
       <c r="J199" t="n">
-        <v>20.1525</v>
+        <v>20.3025</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2571</v>
+        <v>0.3267</v>
       </c>
       <c r="J200" t="n">
-        <v>6.4275</v>
+        <v>8.1675</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.71</v>
+        <v>-0.653</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.75</v>
+        <v>-16.325</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.076</v>
+        <v>0.0333</v>
       </c>
       <c r="J202" t="n">
-        <v>1.748</v>
+        <v>0.7659</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.77</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.3289</v>
+        <v>-0.2404</v>
       </c>
       <c r="J203" t="n">
-        <v>-7.5647</v>
+        <v>-5.5292</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3537</v>
+        <v>-0.2494</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.1351</v>
+        <v>-5.7362</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.65</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5288</v>
+        <v>-0.3525</v>
       </c>
       <c r="J205" t="n">
-        <v>-12.1624</v>
+        <v>-8.1075</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5288</v>
+        <v>-0.3525</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.1624</v>
+        <v>-8.1075</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2826</v>
+        <v>1.1862</v>
       </c>
       <c r="J207" t="n">
-        <v>29.4998</v>
+        <v>27.2826</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.39</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9518</v>
+        <v>0.9678</v>
       </c>
       <c r="J208" t="n">
-        <v>21.8914</v>
+        <v>22.2594</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.23</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5425</v>
+        <v>0.6179</v>
       </c>
       <c r="J209" t="n">
-        <v>12.4775</v>
+        <v>14.2117</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.19</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4404</v>
+        <v>0.5212</v>
       </c>
       <c r="J210" t="n">
-        <v>10.1292</v>
+        <v>11.9876</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.0208</v>
+        <v>0.0998</v>
       </c>
       <c r="J211" t="n">
-        <v>0.4784</v>
+        <v>2.2954</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.09</v>
       </c>
       <c r="I212" t="n">
-        <v>2.0547</v>
+        <v>1.7741</v>
       </c>
       <c r="J212" t="n">
-        <v>39.0393</v>
+        <v>33.7079</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.52</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1375</v>
+        <v>1.1214</v>
       </c>
       <c r="J213" t="n">
-        <v>21.6125</v>
+        <v>21.3066</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.36</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7612</v>
+        <v>0.8784</v>
       </c>
       <c r="J214" t="n">
-        <v>14.4628</v>
+        <v>16.6896</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.28</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.6995</v>
       </c>
       <c r="J215" t="n">
-        <v>11.0808</v>
+        <v>13.2905</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.02</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.096</v>
+        <v>-0.0102</v>
       </c>
       <c r="J216" t="n">
-        <v>-1.824</v>
+        <v>-0.1938</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.88</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1105</v>
+        <v>-0.1127</v>
       </c>
       <c r="J217" t="n">
-        <v>-2.0995</v>
+        <v>-2.1413</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.75</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3226</v>
+        <v>-0.2515</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.1294</v>
+        <v>-4.7785</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.71</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3933</v>
+        <v>-0.2891</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.4727</v>
+        <v>-5.4929</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.7</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4183</v>
+        <v>-0.2977</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.9477</v>
+        <v>-5.6563</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7388</v>
+        <v>-0.5021</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.0372</v>
+        <v>-9.539899999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.45</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1605</v>
+        <v>1.0968</v>
       </c>
       <c r="J222" t="n">
-        <v>29.0125</v>
+        <v>27.42</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2847</v>
+        <v>0.3197</v>
       </c>
       <c r="J223" t="n">
-        <v>7.1175</v>
+        <v>7.9925</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.07</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1881</v>
+        <v>0.2335</v>
       </c>
       <c r="J224" t="n">
-        <v>4.7025</v>
+        <v>5.8375</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0907</v>
+        <v>-0.0286</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.2675</v>
+        <v>-0.715</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1501</v>
+        <v>-0.0835</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.7525</v>
+        <v>-2.0875</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.9</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1881</v>
+        <v>1.3444</v>
       </c>
       <c r="J227" t="n">
-        <v>29.7025</v>
+        <v>33.61</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.01</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0404</v>
+        <v>0.0377</v>
       </c>
       <c r="J228" t="n">
-        <v>1.01</v>
+        <v>0.9425</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.83</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3395</v>
+        <v>-0.2086</v>
       </c>
       <c r="J229" t="n">
-        <v>-8.487500000000001</v>
+        <v>-5.215</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.67</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5589</v>
+        <v>-0.3645</v>
       </c>
       <c r="J230" t="n">
-        <v>-13.9725</v>
+        <v>-9.112500000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6579</v>
+        <v>-0.4384</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.4475</v>
+        <v>-10.96</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.38</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0104</v>
+        <v>0.9918</v>
       </c>
       <c r="J232" t="n">
-        <v>26.2704</v>
+        <v>25.7868</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.3</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8327</v>
+        <v>0.8165</v>
       </c>
       <c r="J233" t="n">
-        <v>21.6502</v>
+        <v>21.229</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.23</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6653</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="J234" t="n">
-        <v>17.2978</v>
+        <v>16.8662</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.15</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4497</v>
+        <v>0.4492</v>
       </c>
       <c r="J235" t="n">
-        <v>11.6922</v>
+        <v>11.6792</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.58</v>
       </c>
       <c r="I236" t="n">
-        <v>-1.1922</v>
+        <v>-1.1931</v>
       </c>
       <c r="J236" t="n">
-        <v>-30.9972</v>
+        <v>-31.0206</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.33</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5596</v>
+        <v>0.6698</v>
       </c>
       <c r="J237" t="n">
-        <v>14.5496</v>
+        <v>17.4148</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2456</v>
+        <v>0.2671</v>
       </c>
       <c r="J238" t="n">
-        <v>6.3856</v>
+        <v>6.9446</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1752</v>
+        <v>0.184</v>
       </c>
       <c r="J239" t="n">
-        <v>4.5552</v>
+        <v>4.784</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.79</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3975</v>
+        <v>-0.2488</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.335</v>
+        <v>-6.4688</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5329</v>
+        <v>-0.3455</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.8554</v>
+        <v>-8.983000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.29</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5265</v>
+        <v>0.6227</v>
       </c>
       <c r="J242" t="n">
-        <v>15.2685</v>
+        <v>18.0583</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0483</v>
       </c>
       <c r="J243" t="n">
-        <v>2.001</v>
+        <v>1.4007</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.96</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.059</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.1866</v>
+        <v>-1.711</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.78</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3986</v>
+        <v>-0.2522</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.5594</v>
+        <v>-7.3138</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.68</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5356</v>
+        <v>-0.3486</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.5324</v>
+        <v>-10.1094</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8327</v>
+        <v>0.8165</v>
       </c>
       <c r="J247" t="n">
-        <v>24.1483</v>
+        <v>23.6785</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.19</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5622</v>
+        <v>0.5501</v>
       </c>
       <c r="J248" t="n">
-        <v>16.3038</v>
+        <v>15.9529</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.17</v>
       </c>
       <c r="I249" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4999</v>
       </c>
       <c r="J249" t="n">
-        <v>14.7204</v>
+        <v>14.4971</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.05</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1182</v>
+        <v>0.17</v>
       </c>
       <c r="J250" t="n">
-        <v>3.4278</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3652</v>
+        <v>-0.2952</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.5908</v>
+        <v>-8.5608</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.94</v>
       </c>
       <c r="I252" t="n">
-        <v>1.9138</v>
+        <v>1.6147</v>
       </c>
       <c r="J252" t="n">
-        <v>42.1036</v>
+        <v>35.5234</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.45</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0037</v>
+        <v>1.0402</v>
       </c>
       <c r="J253" t="n">
-        <v>22.0814</v>
+        <v>22.8844</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.45</v>
       </c>
       <c r="I254" t="n">
-        <v>1.0037</v>
+        <v>1.0402</v>
       </c>
       <c r="J254" t="n">
-        <v>22.0814</v>
+        <v>22.8844</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.21</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4336</v>
+        <v>0.5404</v>
       </c>
       <c r="J255" t="n">
-        <v>9.539199999999999</v>
+        <v>11.8888</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.05</v>
       </c>
       <c r="I256" t="n">
-        <v>0.0136</v>
+        <v>0.1017</v>
       </c>
       <c r="J256" t="n">
-        <v>0.2992</v>
+        <v>2.2374</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.91</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0832</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J257" t="n">
-        <v>-1.8304</v>
+        <v>-1.9866</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1008</v>
+        <v>-0.1022</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.2176</v>
+        <v>-2.2484</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.72</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4198</v>
+        <v>-0.2855</v>
       </c>
       <c r="J259" t="n">
-        <v>-9.2356</v>
+        <v>-6.281</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.72</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4198</v>
+        <v>-0.2855</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.2356</v>
+        <v>-6.281</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.53</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6875</v>
+        <v>-0.4635</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.125</v>
+        <v>-10.197</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2239/event_2239_evp_summary.xlsx
+++ b/database/event/2239/event_2239_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5251</v>
+        <v>6.6934</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3024</v>
+        <v>2.3618</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3077</v>
+        <v>2.4228</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5251</v>
+        <v>6.6934</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9865</v>
+        <v>2.9306</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5386</v>
+        <v>3.7628</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0362</v>
+        <v>4.7751</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6186</v>
+        <v>2.5785</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5386</v>
+        <v>3.7628</v>
       </c>
       <c r="K2" t="n">
         <v>72</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1572</v>
+        <v>6.3413</v>
       </c>
       <c r="N2" t="n">
         <v>229</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7748</v>
+        <v>5.7117</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0377</v>
+        <v>2.0154</v>
       </c>
       <c r="D3" t="n">
-        <v>1.969</v>
+        <v>1.9759</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7748</v>
+        <v>5.7117</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7641</v>
+        <v>2.6619</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0107</v>
+        <v>3.0498</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2527</v>
+        <v>3.8884</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2112</v>
+        <v>2.0997</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0107</v>
+        <v>3.0498</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2219</v>
+        <v>5.1495</v>
       </c>
       <c r="N3" t="n">
         <v>308</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7496</v>
+        <v>4.8008</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6759</v>
+        <v>1.694</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5062</v>
+        <v>1.5612</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7496</v>
+        <v>4.8008</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6667</v>
+        <v>2.5423</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0829</v>
+        <v>2.2585</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9096</v>
+        <v>3.4939</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0328</v>
+        <v>1.8867</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0829</v>
+        <v>2.2585</v>
       </c>
       <c r="K4" t="n">
         <v>125</v>
@@ -621,7 +621,7 @@
         <v>183</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1157</v>
+        <v>4.1452</v>
       </c>
       <c r="N4" t="n">
         <v>308</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2779</v>
+        <v>4.3036</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5095</v>
+        <v>1.5185</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2932</v>
+        <v>1.3349</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2779</v>
+        <v>4.3036</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6089</v>
+        <v>2.516</v>
       </c>
       <c r="G5" t="n">
-        <v>1.669</v>
+        <v>1.7877</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7057</v>
+        <v>3.4069</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9268</v>
+        <v>1.8397</v>
       </c>
       <c r="J5" t="n">
-        <v>1.669</v>
+        <v>1.7877</v>
       </c>
       <c r="K5" t="n">
         <v>72</v>
@@ -667,7 +667,7 @@
         <v>157</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5958</v>
+        <v>3.6274</v>
       </c>
       <c r="N5" t="n">
         <v>229</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1949</v>
+        <v>4.1856</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4802</v>
+        <v>1.4769</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2558</v>
+        <v>1.2812</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1949</v>
+        <v>4.1856</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2039</v>
+        <v>3.2975</v>
       </c>
       <c r="G6" t="n">
-        <v>0.991</v>
+        <v>0.8881</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8022</v>
+        <v>5.9856</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0169</v>
+        <v>3.2322</v>
       </c>
       <c r="J6" t="n">
-        <v>0.991</v>
+        <v>0.8881</v>
       </c>
       <c r="K6" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="L6" t="n">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0079</v>
+        <v>4.1203</v>
       </c>
       <c r="N6" t="n">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1568</v>
+        <v>4.1024</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4667</v>
+        <v>1.4475</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2386</v>
+        <v>1.2433</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1568</v>
+        <v>4.1024</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3757</v>
+        <v>2.8125</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7811</v>
+        <v>1.2899</v>
       </c>
       <c r="H7" t="n">
-        <v>6.4077</v>
+        <v>4.3854</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3317</v>
+        <v>2.3681</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7811</v>
+        <v>1.2899</v>
       </c>
       <c r="K7" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="L7" t="n">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1128</v>
+        <v>3.658</v>
       </c>
       <c r="N7" t="n">
-        <v>208</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0466</v>
+        <v>3.9725</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4279</v>
+        <v>1.4017</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1888</v>
+        <v>1.1842</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0466</v>
+        <v>3.9725</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8615</v>
+        <v>3.0972</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1851</v>
+        <v>0.8753</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5958</v>
+        <v>5.3245</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3896</v>
+        <v>2.8752</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1851</v>
+        <v>0.8753</v>
       </c>
       <c r="K8" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="L8" t="n">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5747</v>
+        <v>3.7505</v>
       </c>
       <c r="N8" t="n">
-        <v>308</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0029</v>
+        <v>2.9326</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0596</v>
+        <v>1.0348</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7176</v>
+        <v>0.7108</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0029</v>
+        <v>2.9326</v>
       </c>
       <c r="F9" t="n">
-        <v>2.682</v>
+        <v>2.5628</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3209</v>
+        <v>0.3698</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9634</v>
+        <v>3.5614</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0608</v>
+        <v>1.9231</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3209</v>
+        <v>0.3698</v>
       </c>
       <c r="K9" t="n">
         <v>101</v>
@@ -851,7 +851,7 @@
         <v>104</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3817</v>
+        <v>2.2929</v>
       </c>
       <c r="N9" t="n">
         <v>205</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9407</v>
+        <v>2.8402</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0376</v>
+        <v>1.0022</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6896</v>
+        <v>0.6687</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9407</v>
+        <v>2.8402</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3511</v>
+        <v>3.2576</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4104</v>
+        <v>-0.4174</v>
       </c>
       <c r="H10" t="n">
-        <v>6.3209</v>
+        <v>5.8538</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2866</v>
+        <v>3.161</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4104</v>
+        <v>-0.4174</v>
       </c>
       <c r="K10" t="n">
         <v>101</v>
@@ -897,7 +897,7 @@
         <v>104</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8762</v>
+        <v>2.7436</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8784</v>
+        <v>2.7691</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0157</v>
+        <v>0.9771</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6614</v>
+        <v>0.6363</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8784</v>
+        <v>2.7691</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4741</v>
+        <v>2.3703</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4043</v>
+        <v>0.3988</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2309</v>
+        <v>2.9263</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6799</v>
+        <v>1.5802</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4043</v>
+        <v>0.3988</v>
       </c>
       <c r="K11" t="n">
         <v>101</v>
@@ -943,7 +943,7 @@
         <v>104</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0842</v>
+        <v>1.979</v>
       </c>
       <c r="N11" t="n">
         <v>205</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.555</v>
+        <v>2.4911</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9015</v>
+        <v>0.879</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5154</v>
+        <v>0.5098</v>
       </c>
       <c r="E12" t="n">
-        <v>2.555</v>
+        <v>2.4911</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3876</v>
+        <v>1.1945</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1674</v>
+        <v>1.2966</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3876</v>
+        <v>1.1945</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7215</v>
+        <v>0.645</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1674</v>
+        <v>1.2966</v>
       </c>
       <c r="K12" t="n">
         <v>125</v>
@@ -989,7 +989,7 @@
         <v>183</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8889</v>
+        <v>1.9416</v>
       </c>
       <c r="N12" t="n">
         <v>308</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4046</v>
+        <v>2.3819</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8485</v>
+        <v>0.8405</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4475</v>
+        <v>0.4601</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4046</v>
+        <v>2.3819</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4046</v>
+        <v>2.3819</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4046</v>
+        <v>2.4882</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4046</v>
+        <v>2.4882</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4046</v>
+        <v>2.4882</v>
       </c>
       <c r="N13" t="n">
         <v>124</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3237</v>
+        <v>2.2163</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8199</v>
+        <v>0.782</v>
       </c>
       <c r="D14" t="n">
-        <v>0.411</v>
+        <v>0.3847</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3237</v>
+        <v>2.2163</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3237</v>
+        <v>2.2163</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3237</v>
+        <v>2.2163</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3237</v>
+        <v>2.2163</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3237</v>
+        <v>2.2163</v>
       </c>
       <c r="N14" t="n">
         <v>126</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1044</v>
+        <v>1.8961</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7425</v>
+        <v>0.669</v>
       </c>
       <c r="D15" t="n">
-        <v>0.312</v>
+        <v>0.2389</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1044</v>
+        <v>1.8961</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8427</v>
+        <v>1.6008</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2617</v>
+        <v>0.2953</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8427</v>
+        <v>1.6008</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9581</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2617</v>
+        <v>0.2953</v>
       </c>
       <c r="K15" t="n">
         <v>130</v>
@@ -1127,7 +1127,7 @@
         <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2198</v>
+        <v>1.1597</v>
       </c>
       <c r="N15" t="n">
         <v>208</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9615</v>
+        <v>1.795</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6921</v>
+        <v>0.6334</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2475</v>
+        <v>0.1929</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9615</v>
+        <v>1.795</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9225</v>
+        <v>1.746</v>
       </c>
       <c r="G16" t="n">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9225</v>
+        <v>1.746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9996</v>
+        <v>0.9428</v>
       </c>
       <c r="J16" t="n">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
       <c r="K16" t="n">
         <v>130</v>
@@ -1173,7 +1173,7 @@
         <v>78</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0386</v>
+        <v>0.9918</v>
       </c>
       <c r="N16" t="n">
         <v>208</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7855</v>
+        <v>1.7084</v>
       </c>
       <c r="C17" t="n">
-        <v>0.63</v>
+        <v>0.6028</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1681</v>
+        <v>0.1535</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7855</v>
+        <v>1.7084</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7855</v>
+        <v>1.7084</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7855</v>
+        <v>1.7084</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7855</v>
+        <v>1.7084</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7855</v>
+        <v>1.7084</v>
       </c>
       <c r="N17" t="n">
         <v>126</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5405</v>
+        <v>1.5487</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5436</v>
+        <v>0.5465</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0574</v>
+        <v>0.0808</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5405</v>
+        <v>1.5487</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2213</v>
+        <v>1.2167</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3192</v>
+        <v>0.332</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2213</v>
+        <v>1.2167</v>
       </c>
       <c r="I18" t="n">
-        <v>0.635</v>
+        <v>0.657</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3192</v>
+        <v>0.332</v>
       </c>
       <c r="K18" t="n">
         <v>130</v>
@@ -1265,7 +1265,7 @@
         <v>78</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9541999999999999</v>
+        <v>0.9890000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>208</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3148</v>
+        <v>1.2622</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4639</v>
+        <v>0.4454</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0444</v>
+        <v>-0.0496</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3148</v>
+        <v>1.2622</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3148</v>
+        <v>1.2622</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3148</v>
+        <v>1.2622</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3148</v>
+        <v>1.2622</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3148</v>
+        <v>1.2622</v>
       </c>
       <c r="N19" t="n">
         <v>111</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2006</v>
+        <v>1.1145</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4236</v>
+        <v>0.3933</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.096</v>
+        <v>-0.1169</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2006</v>
+        <v>1.1145</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2006</v>
+        <v>1.1145</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2006</v>
+        <v>1.1145</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2006</v>
+        <v>1.1145</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2006</v>
+        <v>1.1145</v>
       </c>
       <c r="N20" t="n">
         <v>124</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0499</v>
+        <v>1.0036</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3705</v>
+        <v>0.3541</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.164</v>
+        <v>-0.1673</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0499</v>
+        <v>1.0036</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0499</v>
+        <v>1.0036</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0499</v>
+        <v>1.0036</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0499</v>
+        <v>1.0036</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0499</v>
+        <v>1.0036</v>
       </c>
       <c r="N21" t="n">
         <v>126</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0449</v>
+        <v>0.9981</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3687</v>
+        <v>0.3522</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1663</v>
+        <v>-0.1698</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0449</v>
+        <v>0.9981</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0449</v>
+        <v>0.9981</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0449</v>
+        <v>0.9981</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0449</v>
+        <v>0.9981</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0449</v>
+        <v>0.9981</v>
       </c>
       <c r="N22" t="n">
         <v>111</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9282</v>
+        <v>0.8566</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3275</v>
+        <v>0.3023</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.219</v>
+        <v>-0.2343</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9282</v>
+        <v>0.8566</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9282</v>
+        <v>0.8566</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9282</v>
+        <v>0.8566</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9282</v>
+        <v>0.8566</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9282</v>
+        <v>0.8566</v>
       </c>
       <c r="N23" t="n">
         <v>124</v>
@@ -1504,124 +1504,124 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8394</v>
+        <v>0.7751</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2962</v>
+        <v>0.2735</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2591</v>
+        <v>-0.2714</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8394</v>
+        <v>0.7751</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8394</v>
+        <v>2.145</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-1.3699</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8394</v>
+        <v>2.183</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8394</v>
+        <v>1.1788</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-1.3699</v>
       </c>
       <c r="K24" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8394</v>
+        <v>-0.1910999999999998</v>
       </c>
       <c r="N24" t="n">
-        <v>126</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.759</v>
+        <v>0.7492</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2678</v>
+        <v>0.2644</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2954</v>
+        <v>-0.2832</v>
       </c>
       <c r="E25" t="n">
-        <v>0.759</v>
+        <v>0.7492</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1995</v>
+        <v>0.7492</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4405</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2633</v>
+        <v>0.7492</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1768</v>
+        <v>0.7492</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4405</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L25" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2636999999999998</v>
+        <v>0.7492</v>
       </c>
       <c r="N25" t="n">
-        <v>229</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7272</v>
+        <v>0.7242</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2566</v>
+        <v>0.2555</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3097</v>
+        <v>-0.2945</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7272</v>
+        <v>0.7242</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7272</v>
+        <v>0.7242</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7272</v>
+        <v>0.7242</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7272</v>
+        <v>0.7242</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7272</v>
+        <v>0.7242</v>
       </c>
       <c r="N26" t="n">
         <v>126</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6909</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2527</v>
+        <v>0.2438</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3147</v>
+        <v>-0.3097</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6909</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7161999999999999</v>
+        <v>-0.2687</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.9596</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7161999999999999</v>
+        <v>-0.2687</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7161999999999999</v>
+        <v>-0.1451</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.9596</v>
       </c>
       <c r="K27" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.8145</v>
       </c>
       <c r="N27" t="n">
-        <v>75</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5495</v>
+        <v>0.6641</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1939</v>
+        <v>0.2343</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3899</v>
+        <v>-0.3219</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5495</v>
+        <v>0.6641</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3698</v>
+        <v>0.6641</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9193</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3698</v>
+        <v>0.6641</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1923</v>
+        <v>0.6641</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9193</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L28" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.727</v>
+        <v>0.6641</v>
       </c>
       <c r="N28" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5163</v>
+        <v>0.5034</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1822</v>
+        <v>0.1776</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4049</v>
+        <v>-0.395</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5163</v>
+        <v>0.5034</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5163</v>
+        <v>0.5034</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5163</v>
+        <v>0.5034</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5163</v>
+        <v>0.5034</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5163</v>
+        <v>0.5034</v>
       </c>
       <c r="N29" t="n">
         <v>111</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4409</v>
+        <v>0.3799</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1556</v>
+        <v>0.134</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.439</v>
+        <v>-0.4513</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4409</v>
+        <v>0.3799</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4409</v>
+        <v>0.3799</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4409</v>
+        <v>0.3799</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4409</v>
+        <v>0.3799</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4409</v>
+        <v>0.3799</v>
       </c>
       <c r="N30" t="n">
         <v>124</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3589</v>
+        <v>0.3091</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1266</v>
+        <v>0.1091</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.476</v>
+        <v>-0.4835</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3589</v>
+        <v>0.3091</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3179</v>
+        <v>0.2754</v>
       </c>
       <c r="G31" t="n">
-        <v>0.041</v>
+        <v>0.0337</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3179</v>
+        <v>0.2754</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1653</v>
+        <v>0.1487</v>
       </c>
       <c r="J31" t="n">
-        <v>0.041</v>
+        <v>0.0337</v>
       </c>
       <c r="K31" t="n">
         <v>130</v>
@@ -1863,7 +1863,7 @@
         <v>78</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2063</v>
+        <v>0.1824</v>
       </c>
       <c r="N31" t="n">
         <v>208</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1898</v>
+        <v>0.1939</v>
       </c>
       <c r="C32" t="n">
-        <v>0.067</v>
+        <v>0.0684</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5523</v>
+        <v>-0.5359</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1898</v>
+        <v>0.1939</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1898</v>
+        <v>0.1939</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1898</v>
+        <v>0.1939</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1898</v>
+        <v>0.1939</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1898</v>
+        <v>0.1939</v>
       </c>
       <c r="N32" t="n">
         <v>111</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>wenton</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1802</v>
+        <v>0.1271</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0636</v>
+        <v>0.0448</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5567</v>
+        <v>-0.5663</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1802</v>
+        <v>0.1271</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1802</v>
+        <v>0.1271</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1802</v>
+        <v>0.1271</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1802</v>
+        <v>0.1271</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1802</v>
+        <v>0.1271</v>
       </c>
       <c r="N33" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>wenton</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1535</v>
+        <v>0.1238</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0542</v>
+        <v>0.0437</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5687</v>
+        <v>-0.5678</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1535</v>
+        <v>0.1238</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1535</v>
+        <v>0.1238</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1535</v>
+        <v>0.1238</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1535</v>
+        <v>0.1238</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1535</v>
+        <v>0.1238</v>
       </c>
       <c r="N34" t="n">
-        <v>75</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1092</v>
+        <v>0.1153</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0385</v>
+        <v>0.0407</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.5887</v>
+        <v>-0.5717</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1092</v>
+        <v>0.1153</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5024</v>
+        <v>0.457</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.3932</v>
+        <v>-0.3417</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5024</v>
+        <v>0.457</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2612</v>
+        <v>0.2468</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3932</v>
+        <v>-0.3417</v>
       </c>
       <c r="K35" t="n">
         <v>101</v>
@@ -2047,7 +2047,7 @@
         <v>104</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.132</v>
+        <v>-0.09490000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>205</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3643</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1232</v>
+        <v>-0.1285</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7957</v>
+        <v>-0.79</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3643</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3643</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3643</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3643</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3492</v>
+        <v>-0.3643</v>
       </c>
       <c r="N36" t="n">
         <v>111</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.3925</v>
+        <v>-0.4411</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1385</v>
+        <v>-0.1556</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8152</v>
+        <v>-0.825</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.3925</v>
+        <v>-0.4411</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3925</v>
+        <v>-0.4411</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3925</v>
+        <v>-0.4411</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3925</v>
+        <v>-0.4411</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.3925</v>
+        <v>-0.4411</v>
       </c>
       <c r="N37" t="n">
         <v>75</v>
@@ -2148,78 +2148,78 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.905</v>
+        <v>-0.9369</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3193</v>
+        <v>-0.3306</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0466</v>
+        <v>-1.0507</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.905</v>
+        <v>-0.9369</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.905</v>
+        <v>-1.773</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.8361</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.905</v>
+        <v>-1.773</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.905</v>
+        <v>-0.9574</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.8361</v>
       </c>
       <c r="K38" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.905</v>
+        <v>-0.1213000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>75</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0205</v>
+        <v>-0.9517</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3601</v>
+        <v>-0.3358</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0987</v>
+        <v>-1.0574</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0205</v>
+        <v>-0.9517</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0205</v>
+        <v>-0.9517</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0205</v>
+        <v>-0.9517</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0205</v>
+        <v>-0.9517</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0205</v>
+        <v>-0.9517</v>
       </c>
       <c r="N39" t="n">
         <v>75</v>
@@ -2240,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1511</v>
+        <v>-1.0644</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4062</v>
+        <v>-0.3756</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1577</v>
+        <v>-1.1087</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1511</v>
+        <v>-1.0644</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8992</v>
+        <v>-1.0644</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7481</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8992</v>
+        <v>-1.0644</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9875</v>
+        <v>-1.0644</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7481</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="L40" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.2394000000000001</v>
+        <v>-1.0644</v>
       </c>
       <c r="N40" t="n">
-        <v>308</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.38</v>
+        <v>-4.7991</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.8984</v>
+        <v>-1.6934</v>
       </c>
       <c r="D41" t="n">
-        <v>-3.0668</v>
+        <v>-2.8089</v>
       </c>
       <c r="E41" t="n">
-        <v>-5.38</v>
+        <v>-4.7991</v>
       </c>
       <c r="F41" t="n">
-        <v>-5.6588</v>
+        <v>-5.093</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2788</v>
+        <v>0.2939</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.6588</v>
+        <v>-5.093</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.9423</v>
+        <v>-2.7502</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2788</v>
+        <v>0.2939</v>
       </c>
       <c r="K41" t="n">
         <v>101</v>
@@ -2323,7 +2323,7 @@
         <v>104</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.6635</v>
+        <v>-2.4563</v>
       </c>
       <c r="N41" t="n">
         <v>205</v>
@@ -2429,10 +2429,10 @@
         <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0246</v>
+        <v>-0.0054</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4674</v>
+        <v>-0.1026</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.78</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2132</v>
+        <v>-0.2367</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.0508</v>
+        <v>-4.4973</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2339</v>
+        <v>-0.2569</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.4441</v>
+        <v>-4.8811</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.49</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4865</v>
+        <v>-0.4983</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.243499999999999</v>
+        <v>-9.467700000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.33</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6369</v>
+        <v>-0.6378</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.1011</v>
+        <v>-12.1182</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.34</v>
       </c>
       <c r="I7" t="n">
-        <v>1.211</v>
+        <v>1.3079</v>
       </c>
       <c r="J7" t="n">
-        <v>23.009</v>
+        <v>24.8501</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.95</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9915</v>
+        <v>0.9856</v>
       </c>
       <c r="J8" t="n">
-        <v>18.8385</v>
+        <v>18.7264</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.47</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5434</v>
+        <v>0.5588</v>
       </c>
       <c r="J9" t="n">
-        <v>10.3246</v>
+        <v>10.6172</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.37</v>
+        <v>0.3936</v>
       </c>
       <c r="J10" t="n">
-        <v>7.03</v>
+        <v>7.4784</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.03</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0016</v>
+        <v>0.023</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0304</v>
+        <v>0.437</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.74</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3978</v>
+        <v>1.5111</v>
       </c>
       <c r="J12" t="n">
-        <v>33.5472</v>
+        <v>36.2664</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.56</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1828</v>
+        <v>1.2084</v>
       </c>
       <c r="J13" t="n">
-        <v>28.3872</v>
+        <v>29.0016</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.32</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>19.392</v>
+        <v>18.5208</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.09</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2367</v>
+        <v>0.2579</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6808</v>
+        <v>6.1896</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2367</v>
+        <v>0.2579</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6808</v>
+        <v>6.1896</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.41</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9315</v>
+        <v>0.8616</v>
       </c>
       <c r="J17" t="n">
-        <v>22.356</v>
+        <v>20.6784</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.74</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2714</v>
+        <v>-0.2897</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.5136</v>
+        <v>-6.9528</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.67</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3378</v>
+        <v>-0.3541</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.107200000000001</v>
+        <v>-8.4984</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.64</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3661</v>
+        <v>-0.3812</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.7864</v>
+        <v>-9.1488</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4963</v>
+        <v>-0.5047</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.9112</v>
+        <v>-12.1128</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.37</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9935</v>
+        <v>0.9285</v>
       </c>
       <c r="J22" t="n">
-        <v>35.766</v>
+        <v>33.426</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5154</v>
+        <v>0.4985</v>
       </c>
       <c r="J23" t="n">
-        <v>18.5544</v>
+        <v>17.946</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1113</v>
+        <v>-0.1116</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.0068</v>
+        <v>-4.0176</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1833</v>
+        <v>-0.1818</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.5988</v>
+        <v>-6.5448</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4266</v>
+        <v>-0.4085</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.3576</v>
+        <v>-14.706</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5395</v>
       </c>
       <c r="J27" t="n">
-        <v>19.8324</v>
+        <v>19.422</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2374</v>
+        <v>0.246</v>
       </c>
       <c r="J28" t="n">
-        <v>8.5464</v>
+        <v>8.856</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0612</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>2.2032</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1274</v>
+        <v>-0.1388</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.5864</v>
+        <v>-4.9968</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1387</v>
+        <v>-0.1504</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.9932</v>
+        <v>-5.4144</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.44</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4763</v>
+        <v>0.541</v>
       </c>
       <c r="J32" t="n">
-        <v>16.6705</v>
+        <v>18.935</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2142</v>
+        <v>0.2304</v>
       </c>
       <c r="J33" t="n">
-        <v>7.497</v>
+        <v>8.064</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1329</v>
+        <v>0.1482</v>
       </c>
       <c r="J34" t="n">
-        <v>4.6515</v>
+        <v>5.187</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0104</v>
+        <v>-0.008</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.364</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.92</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1241</v>
+        <v>-0.1333</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.3435</v>
+        <v>-4.6655</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2428</v>
+        <v>0.2522</v>
       </c>
       <c r="J37" t="n">
-        <v>8.497999999999999</v>
+        <v>8.827</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1674</v>
+        <v>0.1783</v>
       </c>
       <c r="J38" t="n">
-        <v>5.859</v>
+        <v>6.2405</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.026</v>
+        <v>0.0319</v>
       </c>
       <c r="J39" t="n">
-        <v>0.91</v>
+        <v>1.1165</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>0.026</v>
+        <v>0.0319</v>
       </c>
       <c r="J40" t="n">
-        <v>0.91</v>
+        <v>1.1165</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.91</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1266</v>
+        <v>-0.1381</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.431</v>
+        <v>-4.8335</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4586</v>
+        <v>0.5079</v>
       </c>
       <c r="J42" t="n">
-        <v>21.0956</v>
+        <v>23.3634</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1385</v>
+        <v>0.1473</v>
       </c>
       <c r="J43" t="n">
-        <v>6.371</v>
+        <v>6.7758</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0504</v>
+        <v>-0.0585</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.3184</v>
+        <v>-2.691</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0885</v>
+        <v>-0.0993</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.071</v>
+        <v>-4.5678</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2395</v>
+        <v>-0.2528</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.017</v>
+        <v>-11.6288</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5101</v>
+        <v>0.5619</v>
       </c>
       <c r="J47" t="n">
-        <v>23.4646</v>
+        <v>25.8474</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.451</v>
+        <v>0.4956</v>
       </c>
       <c r="J48" t="n">
-        <v>20.746</v>
+        <v>22.7976</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2958</v>
+        <v>0.2988</v>
       </c>
       <c r="J49" t="n">
-        <v>13.6068</v>
+        <v>13.7448</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.09</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2958</v>
+        <v>0.2988</v>
       </c>
       <c r="J50" t="n">
-        <v>13.6068</v>
+        <v>13.7448</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.92</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3181</v>
+        <v>-0.3071</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.6326</v>
+        <v>-14.1266</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.19</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4533</v>
+        <v>0.4857</v>
       </c>
       <c r="J52" t="n">
-        <v>10.4259</v>
+        <v>11.1711</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2762</v>
+        <v>0.2595</v>
       </c>
       <c r="J53" t="n">
-        <v>6.3526</v>
+        <v>5.9685</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.65</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3519</v>
+        <v>-0.3685</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.0937</v>
+        <v>-8.4755</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.54</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4548</v>
+        <v>-0.4663</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.4604</v>
+        <v>-10.7249</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.35</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.63</v>
+        <v>-0.6299</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.49</v>
+        <v>-14.4877</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.67</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0349</v>
+        <v>1.1434</v>
       </c>
       <c r="J57" t="n">
-        <v>23.8027</v>
+        <v>26.2982</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.5</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8314</v>
+        <v>0.9251</v>
       </c>
       <c r="J58" t="n">
-        <v>19.1222</v>
+        <v>21.2773</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.31</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5967</v>
+        <v>0.6675</v>
       </c>
       <c r="J59" t="n">
-        <v>13.7241</v>
+        <v>15.3525</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.25</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5157</v>
+        <v>0.5774</v>
       </c>
       <c r="J60" t="n">
-        <v>11.8611</v>
+        <v>13.2802</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.23</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4877</v>
+        <v>0.5462</v>
       </c>
       <c r="J61" t="n">
-        <v>11.2171</v>
+        <v>12.5626</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3308</v>
+        <v>0.3271</v>
       </c>
       <c r="J62" t="n">
-        <v>7.6084</v>
+        <v>7.5233</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0058</v>
+        <v>-0.0062</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1334</v>
+        <v>-0.1426</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.73</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.285</v>
+        <v>-0.3021</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.555</v>
+        <v>-6.9483</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3421</v>
+        <v>-0.3575</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.8683</v>
+        <v>-8.2225</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.445</v>
+        <v>-0.4556</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.235</v>
+        <v>-10.4788</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.81</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6825</v>
+        <v>0.785</v>
       </c>
       <c r="J67" t="n">
-        <v>15.6975</v>
+        <v>18.055</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3381</v>
+        <v>0.3618</v>
       </c>
       <c r="J68" t="n">
-        <v>7.7763</v>
+        <v>8.321400000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.25</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3292</v>
+        <v>0.3505</v>
       </c>
       <c r="J69" t="n">
-        <v>7.5716</v>
+        <v>8.061500000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.16</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2215</v>
+        <v>0.2422</v>
       </c>
       <c r="J70" t="n">
-        <v>5.0945</v>
+        <v>5.5706</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0301</v>
+        <v>0.0477</v>
       </c>
       <c r="J71" t="n">
-        <v>0.6923</v>
+        <v>1.0971</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2.04</v>
       </c>
       <c r="I72" t="n">
-        <v>1.5183</v>
+        <v>1.6427</v>
       </c>
       <c r="J72" t="n">
-        <v>44.0307</v>
+        <v>47.6383</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5062</v>
+        <v>0.5621</v>
       </c>
       <c r="J73" t="n">
-        <v>14.6798</v>
+        <v>16.3009</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.08</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2386</v>
+        <v>0.2523</v>
       </c>
       <c r="J74" t="n">
-        <v>6.9194</v>
+        <v>7.3167</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2891</v>
+        <v>-0.2723</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.383900000000001</v>
+        <v>-7.8967</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.84</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5763</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.7127</v>
+        <v>-15.5382</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.19</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3883</v>
+        <v>0.4199</v>
       </c>
       <c r="J77" t="n">
-        <v>11.2607</v>
+        <v>12.1771</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3662</v>
+        <v>0.3859</v>
       </c>
       <c r="J78" t="n">
-        <v>10.6198</v>
+        <v>11.1911</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.91</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1211</v>
+        <v>-0.1339</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.5119</v>
+        <v>-3.8831</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1323</v>
+        <v>-0.1454</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.8367</v>
+        <v>-4.2166</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2959</v>
+        <v>-0.3088</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.581099999999999</v>
+        <v>-8.9552</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.62</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0224</v>
+        <v>1.1215</v>
       </c>
       <c r="J82" t="n">
-        <v>26.5824</v>
+        <v>29.159</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.14</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3807</v>
+        <v>0.4109</v>
       </c>
       <c r="J83" t="n">
-        <v>9.898199999999999</v>
+        <v>10.6834</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3047</v>
+        <v>0.3118</v>
       </c>
       <c r="J84" t="n">
-        <v>7.9222</v>
+        <v>8.1068</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.1</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3047</v>
+        <v>0.3118</v>
       </c>
       <c r="J85" t="n">
-        <v>7.9222</v>
+        <v>8.1068</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.101</v>
+        <v>-0.0916</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.626</v>
+        <v>-2.3816</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.03</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1134</v>
+        <v>0.1156</v>
       </c>
       <c r="J87" t="n">
-        <v>2.9484</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.03</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1134</v>
+        <v>0.1156</v>
       </c>
       <c r="J88" t="n">
-        <v>2.9484</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.87</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1567</v>
+        <v>-0.1723</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.0742</v>
+        <v>-4.4798</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1671</v>
+        <v>-0.1829</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.3446</v>
+        <v>-4.7554</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.76</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2676</v>
+        <v>-0.2828</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.9576</v>
+        <v>-7.3528</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.51</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9003</v>
+        <v>0.8619</v>
       </c>
       <c r="J92" t="n">
-        <v>27.009</v>
+        <v>25.857</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.32</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5994</v>
+        <v>0.5904</v>
       </c>
       <c r="J93" t="n">
-        <v>17.982</v>
+        <v>17.712</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1985</v>
+        <v>0.2132</v>
       </c>
       <c r="J94" t="n">
-        <v>5.955</v>
+        <v>6.396</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1128</v>
+        <v>0.1289</v>
       </c>
       <c r="J95" t="n">
-        <v>3.384</v>
+        <v>3.867</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1743</v>
+        <v>-0.1835</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.229</v>
+        <v>-5.505</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.47</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1572</v>
+        <v>1.1109</v>
       </c>
       <c r="J97" t="n">
-        <v>34.716</v>
+        <v>33.327</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.96</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1694</v>
+        <v>-0.1722</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.082</v>
+        <v>-5.166</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.95</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2025</v>
+        <v>-0.2039</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.075</v>
+        <v>-6.117</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4116</v>
+        <v>-0.3981</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.348</v>
+        <v>-11.943</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.84</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5214</v>
+        <v>-0.4973</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.642</v>
+        <v>-14.919</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.78</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2506</v>
+        <v>1.2291</v>
       </c>
       <c r="J102" t="n">
-        <v>35.0168</v>
+        <v>34.4148</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.03</v>
       </c>
       <c r="I103" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1055</v>
       </c>
       <c r="J103" t="n">
-        <v>2.7888</v>
+        <v>2.954</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.141</v>
+        <v>-0.1549</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.948</v>
+        <v>-4.3372</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3032</v>
+        <v>-0.3163</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.489599999999999</v>
+        <v>-8.856400000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.38</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.622</v>
+        <v>-0.6199</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.416</v>
+        <v>-17.3572</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.59</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2685</v>
+        <v>1.2376</v>
       </c>
       <c r="J107" t="n">
-        <v>35.518</v>
+        <v>34.6528</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7125</v>
+        <v>0.6792</v>
       </c>
       <c r="J108" t="n">
-        <v>19.95</v>
+        <v>19.0176</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4942</v>
+        <v>0.4839</v>
       </c>
       <c r="J109" t="n">
-        <v>13.8376</v>
+        <v>13.5492</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0175</v>
+        <v>0.034</v>
       </c>
       <c r="J110" t="n">
-        <v>0.49</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.75</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7914</v>
+        <v>-0.7301</v>
       </c>
       <c r="J111" t="n">
-        <v>-22.1592</v>
+        <v>-20.4428</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.68</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3434</v>
+        <v>1.3236</v>
       </c>
       <c r="J112" t="n">
-        <v>32.2416</v>
+        <v>31.7664</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.42</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0172</v>
+        <v>0.9664</v>
       </c>
       <c r="J113" t="n">
-        <v>24.4128</v>
+        <v>23.1936</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.3</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7743</v>
+        <v>0.7398</v>
       </c>
       <c r="J114" t="n">
-        <v>18.5832</v>
+        <v>17.7552</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.18</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4945</v>
+        <v>0.4897</v>
       </c>
       <c r="J115" t="n">
-        <v>11.868</v>
+        <v>11.7528</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.86</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5365</v>
+        <v>-0.4971</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.876</v>
+        <v>-11.9304</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.32</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7711</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J117" t="n">
-        <v>18.5064</v>
+        <v>17.2128</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.98</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0042</v>
+        <v>-0.0181</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.1008</v>
+        <v>-0.4344</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.58</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4213</v>
+        <v>-0.4341</v>
       </c>
       <c r="J119" t="n">
-        <v>-10.1112</v>
+        <v>-10.4184</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4493</v>
+        <v>-0.4605</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.7832</v>
+        <v>-11.052</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.5</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4955</v>
+        <v>-0.5041</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.892</v>
+        <v>-12.0984</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7719</v>
+        <v>0.7368</v>
       </c>
       <c r="J122" t="n">
-        <v>23.157</v>
+        <v>22.104</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.06</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1622</v>
+        <v>0.1704</v>
       </c>
       <c r="J123" t="n">
-        <v>4.866</v>
+        <v>5.112</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.89</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.145</v>
+        <v>-0.1581</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.35</v>
+        <v>-4.743</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.84</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1981</v>
+        <v>-0.2117</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.943</v>
+        <v>-6.351</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2287</v>
+        <v>-0.2423</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.861</v>
+        <v>-7.269</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.37</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9766</v>
+        <v>0.9135</v>
       </c>
       <c r="J127" t="n">
-        <v>29.298</v>
+        <v>27.405</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6026</v>
+        <v>0.5794</v>
       </c>
       <c r="J128" t="n">
-        <v>18.078</v>
+        <v>17.382</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.19</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5528</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>16.584</v>
+        <v>16.044</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>2.043</v>
+        <v>2.463</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.8</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6546</v>
+        <v>-0.6109</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.638</v>
+        <v>-18.327</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.37</v>
       </c>
       <c r="I132" t="n">
-        <v>0.729</v>
+        <v>0.6998</v>
       </c>
       <c r="J132" t="n">
-        <v>20.412</v>
+        <v>19.5944</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2416</v>
+        <v>0.2491</v>
       </c>
       <c r="J133" t="n">
-        <v>6.7648</v>
+        <v>6.9748</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.05</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1356</v>
+        <v>0.1452</v>
       </c>
       <c r="J134" t="n">
-        <v>3.7968</v>
+        <v>4.0656</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.96</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.8256</v>
+        <v>-2.072</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.62</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.413</v>
+        <v>-0.4213</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.564</v>
+        <v>-11.7964</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.31</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8357</v>
+        <v>0.7865</v>
       </c>
       <c r="J137" t="n">
-        <v>23.3996</v>
+        <v>22.022</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4973</v>
+        <v>0.486</v>
       </c>
       <c r="J138" t="n">
-        <v>13.9244</v>
+        <v>13.608</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.316</v>
+        <v>0.3195</v>
       </c>
       <c r="J139" t="n">
-        <v>8.848000000000001</v>
+        <v>8.946</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.259</v>
+        <v>0.2664</v>
       </c>
       <c r="J140" t="n">
-        <v>7.252</v>
+        <v>7.4592</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.04</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1342</v>
+        <v>0.1482</v>
       </c>
       <c r="J141" t="n">
-        <v>3.7576</v>
+        <v>4.1496</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.83</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4932</v>
+        <v>1.4864</v>
       </c>
       <c r="J142" t="n">
-        <v>32.8504</v>
+        <v>32.7008</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.37</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9085</v>
+        <v>0.8619</v>
       </c>
       <c r="J143" t="n">
-        <v>19.987</v>
+        <v>18.9618</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.36</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8875</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>19.525</v>
+        <v>18.5504</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.24</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6166</v>
+        <v>0.6039</v>
       </c>
       <c r="J145" t="n">
-        <v>13.5652</v>
+        <v>13.2858</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.21</v>
       </c>
       <c r="I146" t="n">
-        <v>0.5442</v>
+        <v>0.5393</v>
       </c>
       <c r="J146" t="n">
-        <v>11.9724</v>
+        <v>11.8646</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.86</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.1303</v>
+        <v>-0.1544</v>
       </c>
       <c r="J147" t="n">
-        <v>-2.8666</v>
+        <v>-3.3968</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.75</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2479</v>
+        <v>-0.2697</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.4538</v>
+        <v>-5.9334</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2578</v>
+        <v>-0.2793</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.6716</v>
+        <v>-6.1446</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3866</v>
+        <v>-0.4038</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.5052</v>
+        <v>-8.883599999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.47</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5082</v>
+        <v>-0.5182</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.1804</v>
+        <v>-11.4004</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.16</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3767</v>
+        <v>0.3734</v>
       </c>
       <c r="J152" t="n">
-        <v>9.4175</v>
+        <v>9.335000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.04</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1248</v>
+        <v>0.1309</v>
       </c>
       <c r="J153" t="n">
-        <v>3.12</v>
+        <v>3.2725</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0843</v>
+        <v>-0.0961</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.1075</v>
+        <v>-2.4025</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.93</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.096</v>
+        <v>-0.1084</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.4</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.73</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3029</v>
+        <v>-0.3161</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.5725</v>
+        <v>-7.9025</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.27</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7552</v>
+        <v>0.7133</v>
       </c>
       <c r="J157" t="n">
-        <v>18.88</v>
+        <v>17.8325</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.15</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4555</v>
+        <v>0.446</v>
       </c>
       <c r="J158" t="n">
-        <v>11.3875</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.403</v>
+        <v>0.3982</v>
       </c>
       <c r="J159" t="n">
-        <v>10.075</v>
+        <v>9.955</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0229</v>
+        <v>-0.0157</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.5725</v>
+        <v>-0.3925</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.95</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2242</v>
+        <v>-0.219</v>
       </c>
       <c r="J161" t="n">
-        <v>-5.605</v>
+        <v>-5.475</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1639</v>
+        <v>1.1337</v>
       </c>
       <c r="J162" t="n">
-        <v>26.7697</v>
+        <v>26.0751</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.4</v>
       </c>
       <c r="I163" t="n">
-        <v>0.976</v>
+        <v>0.9242</v>
       </c>
       <c r="J163" t="n">
-        <v>22.448</v>
+        <v>21.2566</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.34</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8548</v>
+        <v>0.8123</v>
       </c>
       <c r="J164" t="n">
-        <v>19.6604</v>
+        <v>18.6829</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.26</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6783</v>
+        <v>0.6558</v>
       </c>
       <c r="J165" t="n">
-        <v>15.6009</v>
+        <v>15.0834</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.11</v>
       </c>
       <c r="I166" t="n">
-        <v>0.3003</v>
+        <v>0.3151</v>
       </c>
       <c r="J166" t="n">
-        <v>6.9069</v>
+        <v>7.2473</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.13</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3546</v>
+        <v>0.345</v>
       </c>
       <c r="J167" t="n">
-        <v>8.155799999999999</v>
+        <v>7.935</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3339</v>
+        <v>0.3255</v>
       </c>
       <c r="J168" t="n">
-        <v>7.6797</v>
+        <v>7.4865</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.72</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3003</v>
+        <v>-0.3159</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.9069</v>
+        <v>-7.2657</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3194</v>
+        <v>-0.3345</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.3462</v>
+        <v>-7.6935</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.65</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3668</v>
+        <v>-0.3801</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.436400000000001</v>
+        <v>-8.7423</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.07</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2649</v>
+        <v>0.2511</v>
       </c>
       <c r="J172" t="n">
-        <v>6.3576</v>
+        <v>6.0264</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.92</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.1021</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.0064</v>
+        <v>-2.4504</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3171</v>
+        <v>-0.3345</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.6104</v>
+        <v>-8.028</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.61</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3924</v>
+        <v>-0.4067</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.4176</v>
+        <v>-9.7608</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.61</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3924</v>
+        <v>-0.4067</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.4176</v>
+        <v>-9.7608</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.53</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1593</v>
+        <v>1.1272</v>
       </c>
       <c r="J177" t="n">
-        <v>27.8232</v>
+        <v>27.0528</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.4</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9838</v>
+        <v>0.9306</v>
       </c>
       <c r="J178" t="n">
-        <v>23.6112</v>
+        <v>22.3344</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.3</v>
       </c>
       <c r="I179" t="n">
-        <v>0.774</v>
+        <v>0.7396</v>
       </c>
       <c r="J179" t="n">
-        <v>18.576</v>
+        <v>17.7504</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7524</v>
+        <v>0.7204</v>
       </c>
       <c r="J180" t="n">
-        <v>18.0576</v>
+        <v>17.2896</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3356</v>
+        <v>-0.3123</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.054399999999999</v>
+        <v>-7.4952</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.57</v>
       </c>
       <c r="I182" t="n">
-        <v>1.257</v>
+        <v>1.2229</v>
       </c>
       <c r="J182" t="n">
-        <v>36.453</v>
+        <v>35.4641</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.3</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8224</v>
+        <v>0.7731</v>
       </c>
       <c r="J183" t="n">
-        <v>23.8496</v>
+        <v>22.4199</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4006</v>
+        <v>0.3966</v>
       </c>
       <c r="J184" t="n">
-        <v>11.6174</v>
+        <v>11.5014</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.78</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.7045</v>
+        <v>-0.6554</v>
       </c>
       <c r="J185" t="n">
-        <v>-20.4305</v>
+        <v>-19.0066</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7045</v>
+        <v>-0.6554</v>
       </c>
       <c r="J186" t="n">
-        <v>-20.4305</v>
+        <v>-19.0066</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4433</v>
+        <v>0.4371</v>
       </c>
       <c r="J187" t="n">
-        <v>12.8557</v>
+        <v>12.6759</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.07</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1868</v>
+        <v>0.1939</v>
       </c>
       <c r="J188" t="n">
-        <v>5.4172</v>
+        <v>5.6231</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.04</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1189</v>
+        <v>0.1266</v>
       </c>
       <c r="J189" t="n">
-        <v>3.4481</v>
+        <v>3.6714</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0198</v>
+        <v>-0.0247</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.5742</v>
+        <v>-0.7163</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4002</v>
+        <v>-0.4096</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.6058</v>
+        <v>-11.8784</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.08</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2416</v>
+        <v>0.2391</v>
       </c>
       <c r="J192" t="n">
-        <v>6.04</v>
+        <v>5.9775</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.93</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0887</v>
+        <v>-0.1029</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.2175</v>
+        <v>-2.5725</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1004</v>
+        <v>-0.1151</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.51</v>
+        <v>-2.8775</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.8</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2244</v>
+        <v>-0.241</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.61</v>
+        <v>-6.025</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.67</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.35</v>
+        <v>-0.3637</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.75</v>
+        <v>-9.092499999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0469</v>
+        <v>0.9974</v>
       </c>
       <c r="J197" t="n">
-        <v>26.1725</v>
+        <v>24.935</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.42</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0326</v>
+        <v>0.9806</v>
       </c>
       <c r="J198" t="n">
-        <v>25.815</v>
+        <v>24.515</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.31</v>
       </c>
       <c r="I199" t="n">
-        <v>0.8121</v>
+        <v>0.7701</v>
       </c>
       <c r="J199" t="n">
-        <v>20.3025</v>
+        <v>19.2525</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3267</v>
+        <v>0.3334</v>
       </c>
       <c r="J200" t="n">
-        <v>8.1675</v>
+        <v>8.335000000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.653</v>
+        <v>-0.605</v>
       </c>
       <c r="J201" t="n">
-        <v>-16.325</v>
+        <v>-15.125</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0333</v>
+        <v>0.0083</v>
       </c>
       <c r="J202" t="n">
-        <v>0.7659</v>
+        <v>0.1909</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.77</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2404</v>
+        <v>-0.2599</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.5292</v>
+        <v>-5.9777</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2494</v>
+        <v>-0.2688</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.7362</v>
+        <v>-6.1824</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.65</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3525</v>
+        <v>-0.369</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.1075</v>
+        <v>-8.487</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3525</v>
+        <v>-0.369</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.1075</v>
+        <v>-8.487</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1862</v>
+        <v>1.1557</v>
       </c>
       <c r="J207" t="n">
-        <v>27.2826</v>
+        <v>26.5811</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.39</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9678</v>
+        <v>0.9139</v>
       </c>
       <c r="J208" t="n">
-        <v>22.2594</v>
+        <v>21.0197</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.23</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6179</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
-        <v>14.2117</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.19</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5212</v>
+        <v>0.5133</v>
       </c>
       <c r="J210" t="n">
-        <v>11.9876</v>
+        <v>11.8059</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.0998</v>
+        <v>0.1243</v>
       </c>
       <c r="J211" t="n">
-        <v>2.2954</v>
+        <v>2.8589</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.09</v>
       </c>
       <c r="I212" t="n">
-        <v>1.7741</v>
+        <v>1.7823</v>
       </c>
       <c r="J212" t="n">
-        <v>33.7079</v>
+        <v>33.8637</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.52</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1214</v>
+        <v>1.0917</v>
       </c>
       <c r="J213" t="n">
-        <v>21.3066</v>
+        <v>20.7423</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.36</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8784</v>
+        <v>0.8369</v>
       </c>
       <c r="J214" t="n">
-        <v>16.6896</v>
+        <v>15.9011</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.28</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6995</v>
+        <v>0.6795</v>
       </c>
       <c r="J215" t="n">
-        <v>13.2905</v>
+        <v>12.9105</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.02</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.0102</v>
+        <v>0.0273</v>
       </c>
       <c r="J216" t="n">
-        <v>-0.1938</v>
+        <v>0.5187</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.88</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1127</v>
+        <v>-0.1358</v>
       </c>
       <c r="J217" t="n">
-        <v>-2.1413</v>
+        <v>-2.5802</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.75</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2515</v>
+        <v>-0.2725</v>
       </c>
       <c r="J218" t="n">
-        <v>-4.7785</v>
+        <v>-5.1775</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.71</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2891</v>
+        <v>-0.3092</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.4929</v>
+        <v>-5.8748</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.7</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2977</v>
+        <v>-0.3177</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.6563</v>
+        <v>-6.0363</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5021</v>
+        <v>-0.512</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.539899999999999</v>
+        <v>-9.728</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.45</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0968</v>
+        <v>1.0514</v>
       </c>
       <c r="J222" t="n">
-        <v>27.42</v>
+        <v>26.285</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3197</v>
+        <v>0.322</v>
       </c>
       <c r="J223" t="n">
-        <v>7.9925</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.07</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2335</v>
+        <v>0.2415</v>
       </c>
       <c r="J224" t="n">
-        <v>5.8375</v>
+        <v>6.0375</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0286</v>
+        <v>-0.0196</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.715</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.0835</v>
+        <v>-0.0794</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.0875</v>
+        <v>-1.985</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.9</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3444</v>
+        <v>1.3331</v>
       </c>
       <c r="J227" t="n">
-        <v>33.61</v>
+        <v>33.3275</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.01</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0377</v>
+        <v>0.0433</v>
       </c>
       <c r="J228" t="n">
-        <v>0.9425</v>
+        <v>1.0825</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.83</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2086</v>
+        <v>-0.2222</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.215</v>
+        <v>-5.555</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.67</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3645</v>
+        <v>-0.375</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.112500000000001</v>
+        <v>-9.375</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4384</v>
+        <v>-0.4459</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.96</v>
+        <v>-11.1475</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.38</v>
       </c>
       <c r="I232" t="n">
-        <v>0.9918</v>
+        <v>0.93</v>
       </c>
       <c r="J232" t="n">
-        <v>25.7868</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.3</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8165</v>
+        <v>0.7689</v>
       </c>
       <c r="J233" t="n">
-        <v>21.229</v>
+        <v>19.9914</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.23</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.621</v>
       </c>
       <c r="J234" t="n">
-        <v>16.8662</v>
+        <v>16.146</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.15</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4492</v>
+        <v>0.4417</v>
       </c>
       <c r="J235" t="n">
-        <v>11.6792</v>
+        <v>11.4842</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.58</v>
       </c>
       <c r="I236" t="n">
-        <v>-1.1931</v>
+        <v>-1.0795</v>
       </c>
       <c r="J236" t="n">
-        <v>-31.0206</v>
+        <v>-28.067</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.33</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6698</v>
+        <v>0.645</v>
       </c>
       <c r="J237" t="n">
-        <v>17.4148</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2671</v>
+        <v>0.2722</v>
       </c>
       <c r="J238" t="n">
-        <v>6.9446</v>
+        <v>7.0772</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I239" t="n">
-        <v>0.184</v>
+        <v>0.1919</v>
       </c>
       <c r="J239" t="n">
-        <v>4.784</v>
+        <v>4.9894</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.79</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2488</v>
+        <v>-0.2621</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.4688</v>
+        <v>-6.8146</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3455</v>
+        <v>-0.3567</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.983000000000001</v>
+        <v>-9.2742</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.29</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6227</v>
+        <v>0.5985</v>
       </c>
       <c r="J242" t="n">
-        <v>18.0583</v>
+        <v>17.3565</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0483</v>
+        <v>0.0509</v>
       </c>
       <c r="J243" t="n">
-        <v>1.4007</v>
+        <v>1.4761</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.96</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.059</v>
+        <v>-0.0693</v>
       </c>
       <c r="J244" t="n">
-        <v>-1.711</v>
+        <v>-2.0097</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.78</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2522</v>
+        <v>-0.2668</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.3138</v>
+        <v>-7.7372</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.68</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3486</v>
+        <v>-0.3609</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.1094</v>
+        <v>-10.4661</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8165</v>
+        <v>0.7689</v>
       </c>
       <c r="J247" t="n">
-        <v>23.6785</v>
+        <v>22.2981</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.19</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5501</v>
+        <v>0.533</v>
       </c>
       <c r="J248" t="n">
-        <v>15.9529</v>
+        <v>15.457</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.17</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4999</v>
+        <v>0.4878</v>
       </c>
       <c r="J249" t="n">
-        <v>14.4971</v>
+        <v>14.1462</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.05</v>
       </c>
       <c r="I250" t="n">
-        <v>0.17</v>
+        <v>0.1818</v>
       </c>
       <c r="J250" t="n">
-        <v>4.93</v>
+        <v>5.2722</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2952</v>
+        <v>-0.284</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.5608</v>
+        <v>-8.236000000000001</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.94</v>
       </c>
       <c r="I252" t="n">
-        <v>1.6147</v>
+        <v>1.6146</v>
       </c>
       <c r="J252" t="n">
-        <v>35.5234</v>
+        <v>35.5212</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.45</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0402</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J253" t="n">
-        <v>22.8844</v>
+        <v>21.945</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.45</v>
       </c>
       <c r="I254" t="n">
-        <v>1.0402</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J254" t="n">
-        <v>22.8844</v>
+        <v>21.945</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.21</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5404</v>
+        <v>0.5367</v>
       </c>
       <c r="J255" t="n">
-        <v>11.8888</v>
+        <v>11.8074</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.05</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1017</v>
+        <v>0.1341</v>
       </c>
       <c r="J256" t="n">
-        <v>2.2374</v>
+        <v>2.9502</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.91</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.1102</v>
       </c>
       <c r="J257" t="n">
-        <v>-1.9866</v>
+        <v>-2.4244</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1022</v>
+        <v>-0.1223</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.2484</v>
+        <v>-2.6906</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.72</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2855</v>
+        <v>-0.3045</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.281</v>
+        <v>-6.699</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.72</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2855</v>
+        <v>-0.3045</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.281</v>
+        <v>-6.699</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.53</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4635</v>
+        <v>-0.4746</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.197</v>
+        <v>-10.4412</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2239/event_2239_evp_summary.xlsx
+++ b/database/event/2239/event_2239_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6934</v>
+        <v>6.6751</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3618</v>
+        <v>2.3553</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4228</v>
+        <v>2.435</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6934</v>
+        <v>6.6751</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9306</v>
+        <v>2.9245</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7628</v>
+        <v>3.7506</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7751</v>
+        <v>4.5372</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5785</v>
+        <v>2.5475</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7628</v>
+        <v>3.7506</v>
       </c>
       <c r="K2" t="n">
         <v>72</v>
@@ -529,7 +529,7 @@
         <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>6.3413</v>
+        <v>6.2981</v>
       </c>
       <c r="N2" t="n">
         <v>229</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7117</v>
+        <v>5.6636</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0154</v>
+        <v>1.9984</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9759</v>
+        <v>1.9743</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7117</v>
+        <v>5.6636</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6619</v>
+        <v>2.7258</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0498</v>
+        <v>2.9378</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8884</v>
+        <v>3.7913</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0997</v>
+        <v>2.1287</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0498</v>
+        <v>2.9378</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>183</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1495</v>
+        <v>5.0665</v>
       </c>
       <c r="N3" t="n">
         <v>308</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8008</v>
+        <v>4.759</v>
       </c>
       <c r="C4" t="n">
-        <v>1.694</v>
+        <v>1.6792</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5612</v>
+        <v>1.5622</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8008</v>
+        <v>4.759</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5423</v>
+        <v>2.6087</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2585</v>
+        <v>2.1503</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4939</v>
+        <v>3.3514</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8867</v>
+        <v>1.8817</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2585</v>
+        <v>2.1503</v>
       </c>
       <c r="K4" t="n">
         <v>125</v>
@@ -621,7 +621,7 @@
         <v>183</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1452</v>
+        <v>4.032</v>
       </c>
       <c r="N4" t="n">
         <v>308</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3036</v>
+        <v>4.4028</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5185</v>
+        <v>1.5535</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3349</v>
+        <v>1.3999</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3036</v>
+        <v>4.4028</v>
       </c>
       <c r="F5" t="n">
-        <v>2.516</v>
+        <v>2.5845</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7877</v>
+        <v>1.8183</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4069</v>
+        <v>3.2606</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8397</v>
+        <v>1.8307</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7877</v>
+        <v>1.8183</v>
       </c>
       <c r="K5" t="n">
         <v>72</v>
@@ -667,7 +667,7 @@
         <v>157</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6274</v>
+        <v>3.649</v>
       </c>
       <c r="N5" t="n">
         <v>229</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1856</v>
+        <v>4.1002</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4769</v>
+        <v>1.4468</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2812</v>
+        <v>1.262</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1856</v>
+        <v>4.1002</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2975</v>
+        <v>2.8565</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8881</v>
+        <v>1.2437</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9856</v>
+        <v>4.2818</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2322</v>
+        <v>2.4041</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8881</v>
+        <v>1.2437</v>
       </c>
       <c r="K6" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="L6" t="n">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1203</v>
+        <v>3.6478</v>
       </c>
       <c r="N6" t="n">
-        <v>208</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1024</v>
+        <v>4.0538</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4475</v>
+        <v>1.4304</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2433</v>
+        <v>1.2409</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1024</v>
+        <v>4.0538</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8125</v>
+        <v>3.2532</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2899</v>
+        <v>0.8006</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3854</v>
+        <v>5.7715</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3681</v>
+        <v>3.2405</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2899</v>
+        <v>0.8006</v>
       </c>
       <c r="K7" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="L7" t="n">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="M7" t="n">
-        <v>3.658</v>
+        <v>4.0411</v>
       </c>
       <c r="N7" t="n">
-        <v>308</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9725</v>
+        <v>4.0011</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4017</v>
+        <v>1.4118</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1842</v>
+        <v>1.2169</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9725</v>
+        <v>4.0011</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0972</v>
+        <v>3.0743</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8753</v>
+        <v>0.9268</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3245</v>
+        <v>5.0995</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8752</v>
+        <v>2.8632</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8753</v>
+        <v>0.9268</v>
       </c>
       <c r="K8" t="n">
         <v>72</v>
@@ -805,7 +805,7 @@
         <v>157</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7505</v>
+        <v>3.79</v>
       </c>
       <c r="N8" t="n">
         <v>229</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9326</v>
+        <v>2.9014</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0348</v>
+        <v>1.0238</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7108</v>
+        <v>0.7159</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9326</v>
+        <v>2.9014</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5628</v>
+        <v>2.5995</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3698</v>
+        <v>0.3019</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5614</v>
+        <v>3.3172</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9231</v>
+        <v>1.8625</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3698</v>
+        <v>0.3019</v>
       </c>
       <c r="K9" t="n">
         <v>101</v>
@@ -851,7 +851,7 @@
         <v>104</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2929</v>
+        <v>2.1644</v>
       </c>
       <c r="N9" t="n">
         <v>205</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8402</v>
+        <v>2.7988</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0022</v>
+        <v>0.9876</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6687</v>
+        <v>0.6692</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8402</v>
+        <v>2.7988</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2576</v>
+        <v>3.2282</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4174</v>
+        <v>-0.4294</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8538</v>
+        <v>5.6776</v>
       </c>
       <c r="I10" t="n">
-        <v>3.161</v>
+        <v>3.1878</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4174</v>
+        <v>-0.4294</v>
       </c>
       <c r="K10" t="n">
         <v>101</v>
@@ -897,7 +897,7 @@
         <v>104</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7436</v>
+        <v>2.7584</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7691</v>
+        <v>2.7615</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9771</v>
+        <v>0.9744</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6363</v>
+        <v>0.6522</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7691</v>
+        <v>2.7615</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3703</v>
+        <v>2.4322</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3988</v>
+        <v>0.3293</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9263</v>
+        <v>2.689</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5802</v>
+        <v>1.5098</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3988</v>
+        <v>0.3293</v>
       </c>
       <c r="K11" t="n">
         <v>101</v>
@@ -943,7 +943,7 @@
         <v>104</v>
       </c>
       <c r="M11" t="n">
-        <v>1.979</v>
+        <v>1.8391</v>
       </c>
       <c r="N11" t="n">
         <v>205</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4911</v>
+        <v>2.4358</v>
       </c>
       <c r="C12" t="n">
-        <v>0.879</v>
+        <v>0.8595</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5098</v>
+        <v>0.5038</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4911</v>
+        <v>2.4358</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1945</v>
+        <v>1.2259</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2966</v>
+        <v>1.2099</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1945</v>
+        <v>1.2259</v>
       </c>
       <c r="I12" t="n">
-        <v>0.645</v>
+        <v>0.6883</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2966</v>
+        <v>1.2099</v>
       </c>
       <c r="K12" t="n">
         <v>125</v>
@@ -989,7 +989,7 @@
         <v>183</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9416</v>
+        <v>1.8982</v>
       </c>
       <c r="N12" t="n">
         <v>308</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3819</v>
+        <v>2.3965</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8405</v>
+        <v>0.8456</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4601</v>
+        <v>0.4859</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3819</v>
+        <v>2.3965</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3819</v>
+        <v>2.3965</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4882</v>
+        <v>2.542</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4882</v>
+        <v>2.542</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4882</v>
+        <v>2.542</v>
       </c>
       <c r="N13" t="n">
         <v>124</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2163</v>
+        <v>2.0774</v>
       </c>
       <c r="C14" t="n">
-        <v>0.782</v>
+        <v>0.733</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3847</v>
+        <v>0.3406</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2163</v>
+        <v>2.0774</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2163</v>
+        <v>2.0774</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2163</v>
+        <v>2.0774</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2163</v>
+        <v>2.0774</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2163</v>
+        <v>2.0774</v>
       </c>
       <c r="N14" t="n">
         <v>126</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8961</v>
+        <v>1.6811</v>
       </c>
       <c r="C15" t="n">
-        <v>0.669</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2389</v>
+        <v>0.16</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8961</v>
+        <v>1.6811</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6008</v>
+        <v>1.4385</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2953</v>
+        <v>0.2426</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6008</v>
+        <v>1.4385</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8077</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2953</v>
+        <v>0.2426</v>
       </c>
       <c r="K15" t="n">
         <v>130</v>
@@ -1127,7 +1127,7 @@
         <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1597</v>
+        <v>1.0503</v>
       </c>
       <c r="N15" t="n">
         <v>208</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.795</v>
+        <v>1.6511</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6334</v>
+        <v>0.5826</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1929</v>
+        <v>0.1464</v>
       </c>
       <c r="E16" t="n">
-        <v>1.795</v>
+        <v>1.6511</v>
       </c>
       <c r="F16" t="n">
-        <v>1.746</v>
+        <v>1.6587</v>
       </c>
       <c r="G16" t="n">
-        <v>0.049</v>
+        <v>-0.0076</v>
       </c>
       <c r="H16" t="n">
-        <v>1.746</v>
+        <v>1.6587</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9428</v>
+        <v>0.9313</v>
       </c>
       <c r="J16" t="n">
-        <v>0.049</v>
+        <v>-0.0076</v>
       </c>
       <c r="K16" t="n">
         <v>130</v>
@@ -1173,7 +1173,7 @@
         <v>78</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9918</v>
+        <v>0.9237</v>
       </c>
       <c r="N16" t="n">
         <v>208</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7084</v>
+        <v>1.5876</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6028</v>
+        <v>0.5602</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1535</v>
+        <v>0.1174</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7084</v>
+        <v>1.5876</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7084</v>
+        <v>1.5876</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7084</v>
+        <v>1.5876</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7084</v>
+        <v>1.5876</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7084</v>
+        <v>1.5876</v>
       </c>
       <c r="N17" t="n">
         <v>126</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5487</v>
+        <v>1.2676</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5465</v>
+        <v>0.4473</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0808</v>
+        <v>-0.0283</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5487</v>
+        <v>1.2676</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2167</v>
+        <v>1.002</v>
       </c>
       <c r="G18" t="n">
-        <v>0.332</v>
+        <v>0.2656</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2167</v>
+        <v>1.002</v>
       </c>
       <c r="I18" t="n">
-        <v>0.657</v>
+        <v>0.5626</v>
       </c>
       <c r="J18" t="n">
-        <v>0.332</v>
+        <v>0.2656</v>
       </c>
       <c r="K18" t="n">
         <v>130</v>
@@ -1265,7 +1265,7 @@
         <v>78</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.8282</v>
       </c>
       <c r="N18" t="n">
         <v>208</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2622</v>
+        <v>1.1498</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4454</v>
+        <v>0.4057</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0496</v>
+        <v>-0.082</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2622</v>
+        <v>1.1498</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2622</v>
+        <v>1.1498</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2622</v>
+        <v>1.1498</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2622</v>
+        <v>1.1498</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2622</v>
+        <v>1.1498</v>
       </c>
       <c r="N19" t="n">
         <v>111</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1145</v>
+        <v>1.1446</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3933</v>
+        <v>0.4039</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1169</v>
+        <v>-0.0844</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1145</v>
+        <v>1.1446</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1145</v>
+        <v>1.1446</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1145</v>
+        <v>1.1446</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1145</v>
+        <v>1.1446</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1145</v>
+        <v>1.1446</v>
       </c>
       <c r="N20" t="n">
         <v>124</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0036</v>
+        <v>0.9442</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3541</v>
+        <v>0.3332</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1673</v>
+        <v>-0.1757</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0036</v>
+        <v>0.9442</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0036</v>
+        <v>0.9442</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0036</v>
+        <v>0.9442</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0036</v>
+        <v>0.9442</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0036</v>
+        <v>0.9442</v>
       </c>
       <c r="N21" t="n">
         <v>126</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9981</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3522</v>
+        <v>0.3118</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1698</v>
+        <v>-0.2033</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9981</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9981</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9981</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9981</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9981</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>111</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8566</v>
+        <v>0.778</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3023</v>
+        <v>0.2745</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2343</v>
+        <v>-0.2514</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8566</v>
+        <v>0.778</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8566</v>
+        <v>0.778</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8566</v>
+        <v>0.778</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8566</v>
+        <v>0.778</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8566</v>
+        <v>0.778</v>
       </c>
       <c r="N23" t="n">
         <v>124</v>
@@ -1504,35 +1504,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7751</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2735</v>
+        <v>0.2641</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2714</v>
+        <v>-0.2648</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7751</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>2.145</v>
+        <v>-0.2096</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3699</v>
+        <v>0.9581</v>
       </c>
       <c r="H24" t="n">
-        <v>2.183</v>
+        <v>-0.2096</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1788</v>
+        <v>-0.1177</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3699</v>
+        <v>0.9581</v>
       </c>
       <c r="K24" t="n">
         <v>72</v>
@@ -1541,7 +1541,7 @@
         <v>157</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1910999999999998</v>
+        <v>0.8403999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>229</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7492</v>
+        <v>0.7262</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2644</v>
+        <v>0.2562</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2832</v>
+        <v>-0.275</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7492</v>
+        <v>0.7262</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7492</v>
+        <v>0.7262</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7492</v>
+        <v>0.7262</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7492</v>
+        <v>0.7262</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7492</v>
+        <v>0.7262</v>
       </c>
       <c r="N25" t="n">
         <v>126</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7242</v>
+        <v>0.6097</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2555</v>
+        <v>0.2151</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2945</v>
+        <v>-0.328</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7242</v>
+        <v>0.6097</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7242</v>
+        <v>0.6097</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7242</v>
+        <v>0.6097</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7242</v>
+        <v>0.6097</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7242</v>
+        <v>0.6097</v>
       </c>
       <c r="N26" t="n">
         <v>126</v>
@@ -1642,35 +1642,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6909</v>
+        <v>0.5812</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2438</v>
+        <v>0.2051</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3097</v>
+        <v>-0.341</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6909</v>
+        <v>0.5812</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2687</v>
+        <v>1.9392</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9596</v>
+        <v>-1.358</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2687</v>
+        <v>1.9392</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1451</v>
+        <v>1.0888</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9596</v>
+        <v>-1.358</v>
       </c>
       <c r="K27" t="n">
         <v>72</v>
@@ -1679,7 +1679,7 @@
         <v>157</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8145</v>
+        <v>-0.2692000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>229</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6641</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2343</v>
+        <v>0.2004</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3219</v>
+        <v>-0.347</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6641</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6641</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6641</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6641</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6641</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="N28" t="n">
         <v>75</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5034</v>
+        <v>0.3945</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1776</v>
+        <v>0.1392</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.395</v>
+        <v>-0.4261</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5034</v>
+        <v>0.3945</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5034</v>
+        <v>0.3945</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5034</v>
+        <v>0.3945</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5034</v>
+        <v>0.3945</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5034</v>
+        <v>0.3945</v>
       </c>
       <c r="N29" t="n">
         <v>111</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3799</v>
+        <v>0.382</v>
       </c>
       <c r="C30" t="n">
-        <v>0.134</v>
+        <v>0.1348</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4513</v>
+        <v>-0.4318</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3799</v>
+        <v>0.382</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3799</v>
+        <v>0.382</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3799</v>
+        <v>0.382</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3799</v>
+        <v>0.382</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3799</v>
+        <v>0.382</v>
       </c>
       <c r="N30" t="n">
         <v>124</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3091</v>
+        <v>0.2915</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1091</v>
+        <v>0.1029</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4835</v>
+        <v>-0.473</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3091</v>
+        <v>0.2915</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2754</v>
+        <v>0.2745</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0337</v>
+        <v>0.017</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2754</v>
+        <v>0.2745</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1487</v>
+        <v>0.1541</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0337</v>
+        <v>0.017</v>
       </c>
       <c r="K31" t="n">
         <v>130</v>
@@ -1863,7 +1863,7 @@
         <v>78</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1824</v>
+        <v>0.1711</v>
       </c>
       <c r="N31" t="n">
         <v>208</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1939</v>
+        <v>0.156</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0684</v>
+        <v>0.055</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5359</v>
+        <v>-0.5347</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1939</v>
+        <v>0.156</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1939</v>
+        <v>0.156</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1939</v>
+        <v>0.156</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1939</v>
+        <v>0.156</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1939</v>
+        <v>0.156</v>
       </c>
       <c r="N32" t="n">
         <v>111</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>wenton</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1271</v>
+        <v>0.0796</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0448</v>
+        <v>0.0281</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5663</v>
+        <v>-0.5695</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1271</v>
+        <v>0.0796</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1271</v>
+        <v>0.0796</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1271</v>
+        <v>0.0796</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1271</v>
+        <v>0.0796</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1271</v>
+        <v>0.0796</v>
       </c>
       <c r="N33" t="n">
-        <v>75</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>wenton</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1238</v>
+        <v>0.0736</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0437</v>
+        <v>0.026</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5678</v>
+        <v>-0.5723</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1238</v>
+        <v>0.0736</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1238</v>
+        <v>0.0736</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1238</v>
+        <v>0.0736</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1238</v>
+        <v>0.0736</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1238</v>
+        <v>0.0736</v>
       </c>
       <c r="N34" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1153</v>
+        <v>0.0367</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0407</v>
+        <v>0.0129</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.5717</v>
+        <v>-0.5891</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1153</v>
+        <v>0.0367</v>
       </c>
       <c r="F35" t="n">
-        <v>0.457</v>
+        <v>0.4146</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.3417</v>
+        <v>-0.3779</v>
       </c>
       <c r="H35" t="n">
-        <v>0.457</v>
+        <v>0.4146</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2468</v>
+        <v>0.2328</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3417</v>
+        <v>-0.3779</v>
       </c>
       <c r="K35" t="n">
         <v>101</v>
@@ -2047,7 +2047,7 @@
         <v>104</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.09490000000000001</v>
+        <v>-0.1451</v>
       </c>
       <c r="N35" t="n">
         <v>205</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3643</v>
+        <v>-0.3606</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1285</v>
+        <v>-0.1272</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.79</v>
+        <v>-0.7701</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3643</v>
+        <v>-0.3606</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3643</v>
+        <v>-0.3606</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3643</v>
+        <v>-0.3606</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3643</v>
+        <v>-0.3606</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3643</v>
+        <v>-0.3606</v>
       </c>
       <c r="N36" t="n">
         <v>111</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.4411</v>
+        <v>-0.4067</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1556</v>
+        <v>-0.1435</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.825</v>
+        <v>-0.7911</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.4411</v>
+        <v>-0.4067</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4411</v>
+        <v>-0.4067</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4411</v>
+        <v>-0.4067</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4411</v>
+        <v>-0.4067</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.4411</v>
+        <v>-0.4067</v>
       </c>
       <c r="N37" t="n">
         <v>75</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9369</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3306</v>
+        <v>-0.2968</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0507</v>
+        <v>-0.989</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9369</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.773</v>
+        <v>-1.6038</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8361</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.773</v>
+        <v>-1.6038</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9574</v>
+        <v>-0.9005</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8361</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="K38" t="n">
         <v>125</v>
@@ -2185,7 +2185,7 @@
         <v>183</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.1213000000000001</v>
+        <v>-0.1379</v>
       </c>
       <c r="N38" t="n">
         <v>308</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9517</v>
+        <v>-0.9015</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3358</v>
+        <v>-0.3181</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0574</v>
+        <v>-1.0165</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9517</v>
+        <v>-0.9015</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9517</v>
+        <v>-0.9015</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9517</v>
+        <v>-0.9015</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9517</v>
+        <v>-0.9015</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9517</v>
+        <v>-0.9015</v>
       </c>
       <c r="N39" t="n">
         <v>75</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.0644</v>
+        <v>-1.0204</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3756</v>
+        <v>-0.3601</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1087</v>
+        <v>-1.0706</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.0644</v>
+        <v>-1.0204</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0644</v>
+        <v>-1.0204</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0644</v>
+        <v>-1.0204</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0644</v>
+        <v>-1.0204</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0644</v>
+        <v>-1.0204</v>
       </c>
       <c r="N40" t="n">
         <v>75</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.7991</v>
+        <v>-4.491</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.6934</v>
+        <v>-1.5847</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.8089</v>
+        <v>-2.6517</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.7991</v>
+        <v>-4.491</v>
       </c>
       <c r="F41" t="n">
-        <v>-5.093</v>
+        <v>-4.7908</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2939</v>
+        <v>0.2998</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.093</v>
+        <v>-4.7908</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.7502</v>
+        <v>-2.6899</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2939</v>
+        <v>0.2998</v>
       </c>
       <c r="K41" t="n">
         <v>101</v>
@@ -2323,7 +2323,7 @@
         <v>104</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4563</v>
+        <v>-2.3901</v>
       </c>
       <c r="N41" t="n">
         <v>205</v>
@@ -2429,10 +2429,10 @@
         <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0054</v>
+        <v>0.0146</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1026</v>
+        <v>0.2774</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.78</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2367</v>
+        <v>-0.2224</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.4973</v>
+        <v>-4.2256</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2569</v>
+        <v>-0.2431</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.8811</v>
+        <v>-4.6189</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.49</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4983</v>
+        <v>-0.4963</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.467700000000001</v>
+        <v>-9.4297</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.33</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6378</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.1182</v>
+        <v>-12.4792</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.34</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3079</v>
+        <v>1.2597</v>
       </c>
       <c r="J7" t="n">
-        <v>24.8501</v>
+        <v>23.9343</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.95</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9856</v>
+        <v>0.9195</v>
       </c>
       <c r="J8" t="n">
-        <v>18.7264</v>
+        <v>17.4705</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.47</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5588</v>
+        <v>0.4964</v>
       </c>
       <c r="J9" t="n">
-        <v>10.6172</v>
+        <v>9.4316</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3936</v>
+        <v>0.3384</v>
       </c>
       <c r="J10" t="n">
-        <v>7.4784</v>
+        <v>6.4296</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.03</v>
       </c>
       <c r="I11" t="n">
-        <v>0.023</v>
+        <v>0.0065</v>
       </c>
       <c r="J11" t="n">
-        <v>0.437</v>
+        <v>0.1235</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.74</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5111</v>
+        <v>1.5429</v>
       </c>
       <c r="J12" t="n">
-        <v>36.2664</v>
+        <v>37.0296</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.56</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2084</v>
+        <v>1.2264</v>
       </c>
       <c r="J13" t="n">
-        <v>29.0016</v>
+        <v>29.4336</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.32</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>18.5208</v>
+        <v>18.084</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.09</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2579</v>
+        <v>0.2266</v>
       </c>
       <c r="J15" t="n">
-        <v>6.1896</v>
+        <v>5.4384</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2579</v>
+        <v>0.2266</v>
       </c>
       <c r="J16" t="n">
-        <v>6.1896</v>
+        <v>5.4384</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.41</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8616</v>
+        <v>0.8388</v>
       </c>
       <c r="J17" t="n">
-        <v>20.6784</v>
+        <v>20.1312</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.74</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2897</v>
+        <v>-0.2726</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.9528</v>
+        <v>-6.5424</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.67</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3541</v>
+        <v>-0.3394</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.4984</v>
+        <v>-8.1456</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.64</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3812</v>
+        <v>-0.3683</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.1488</v>
+        <v>-8.8392</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5047</v>
+        <v>-0.5044</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.1128</v>
+        <v>-12.1056</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.37</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9285</v>
+        <v>0.9135</v>
       </c>
       <c r="J22" t="n">
-        <v>33.426</v>
+        <v>32.886</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4985</v>
+        <v>0.4577</v>
       </c>
       <c r="J23" t="n">
-        <v>17.946</v>
+        <v>16.4772</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1116</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.0176</v>
+        <v>-3.078</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1818</v>
+        <v>-0.1478</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.5448</v>
+        <v>-5.3208</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4085</v>
+        <v>-0.3655</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.706</v>
+        <v>-13.158</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5395</v>
+        <v>0.4798</v>
       </c>
       <c r="J27" t="n">
-        <v>19.422</v>
+        <v>17.2728</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.246</v>
+        <v>0.2009</v>
       </c>
       <c r="J28" t="n">
-        <v>8.856</v>
+        <v>7.2324</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="J29" t="n">
-        <v>2.52</v>
+        <v>1.836</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1388</v>
+        <v>-0.1193</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.9968</v>
+        <v>-4.2948</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1504</v>
+        <v>-0.1304</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.4144</v>
+        <v>-4.6944</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.44</v>
       </c>
       <c r="I32" t="n">
-        <v>0.541</v>
+        <v>0.5039</v>
       </c>
       <c r="J32" t="n">
-        <v>18.935</v>
+        <v>17.6365</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2304</v>
+        <v>0.184</v>
       </c>
       <c r="J33" t="n">
-        <v>8.064</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1482</v>
+        <v>0.114</v>
       </c>
       <c r="J34" t="n">
-        <v>5.187</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.008</v>
+        <v>-0.0058</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.28</v>
+        <v>-0.203</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.92</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1333</v>
+        <v>-0.1141</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.6655</v>
+        <v>-3.9935</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2522</v>
+        <v>0.2376</v>
       </c>
       <c r="J37" t="n">
-        <v>8.827</v>
+        <v>8.316000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1783</v>
+        <v>0.162</v>
       </c>
       <c r="J38" t="n">
-        <v>6.2405</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0319</v>
+        <v>0.0248</v>
       </c>
       <c r="J39" t="n">
-        <v>1.1165</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0319</v>
+        <v>0.0248</v>
       </c>
       <c r="J40" t="n">
-        <v>1.1165</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.91</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1381</v>
+        <v>-0.1187</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.8335</v>
+        <v>-4.1545</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5079</v>
+        <v>0.4728</v>
       </c>
       <c r="J42" t="n">
-        <v>23.3634</v>
+        <v>21.7488</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1473</v>
+        <v>0.1135</v>
       </c>
       <c r="J43" t="n">
-        <v>6.7758</v>
+        <v>5.221</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.97</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0585</v>
+        <v>-0.0458</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.691</v>
+        <v>-2.1068</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0993</v>
+        <v>-0.0824</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.5678</v>
+        <v>-3.7904</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2528</v>
+        <v>-0.2329</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.6288</v>
+        <v>-10.7134</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5619</v>
+        <v>0.5512</v>
       </c>
       <c r="J47" t="n">
-        <v>25.8474</v>
+        <v>25.3552</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4956</v>
+        <v>0.4758</v>
       </c>
       <c r="J48" t="n">
-        <v>22.7976</v>
+        <v>21.8868</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2988</v>
+        <v>0.2628</v>
       </c>
       <c r="J49" t="n">
-        <v>13.7448</v>
+        <v>12.0888</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.09</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2988</v>
+        <v>0.2628</v>
       </c>
       <c r="J50" t="n">
-        <v>13.7448</v>
+        <v>12.0888</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.92</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3071</v>
+        <v>-0.2658</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.1266</v>
+        <v>-12.2268</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.19</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4857</v>
+        <v>0.4597</v>
       </c>
       <c r="J52" t="n">
-        <v>11.1711</v>
+        <v>10.5731</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2595</v>
+        <v>0.2216</v>
       </c>
       <c r="J53" t="n">
-        <v>5.9685</v>
+        <v>5.0968</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.65</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3685</v>
+        <v>-0.3549</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.4755</v>
+        <v>-8.162699999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.54</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4663</v>
+        <v>-0.461</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.7249</v>
+        <v>-10.603</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.35</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6299</v>
+        <v>-0.6489</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.4877</v>
+        <v>-14.9247</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.67</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1434</v>
+        <v>1.1371</v>
       </c>
       <c r="J57" t="n">
-        <v>26.2982</v>
+        <v>26.1533</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.5</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9251</v>
+        <v>0.9139</v>
       </c>
       <c r="J58" t="n">
-        <v>21.2773</v>
+        <v>21.0197</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.31</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6675</v>
+        <v>0.661</v>
       </c>
       <c r="J59" t="n">
-        <v>15.3525</v>
+        <v>15.203</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.25</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5774</v>
+        <v>0.5743</v>
       </c>
       <c r="J60" t="n">
-        <v>13.2802</v>
+        <v>13.2089</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.23</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5462</v>
+        <v>0.5441</v>
       </c>
       <c r="J61" t="n">
-        <v>12.5626</v>
+        <v>12.5143</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3271</v>
+        <v>0.323</v>
       </c>
       <c r="J62" t="n">
-        <v>7.5233</v>
+        <v>7.429</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0062</v>
+        <v>-0.0018</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.1426</v>
+        <v>-0.0414</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.73</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3021</v>
+        <v>-0.2848</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.9483</v>
+        <v>-6.5504</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3575</v>
+        <v>-0.3428</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.2225</v>
+        <v>-7.8844</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4556</v>
+        <v>-0.4496</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.4788</v>
+        <v>-10.3408</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.81</v>
       </c>
       <c r="I67" t="n">
-        <v>0.785</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>18.055</v>
+        <v>16.8912</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3618</v>
+        <v>0.3057</v>
       </c>
       <c r="J68" t="n">
-        <v>8.321400000000001</v>
+        <v>7.0311</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.25</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3505</v>
+        <v>0.2954</v>
       </c>
       <c r="J69" t="n">
-        <v>8.061500000000001</v>
+        <v>6.7942</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.16</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2422</v>
+        <v>0.1978</v>
       </c>
       <c r="J70" t="n">
-        <v>5.5706</v>
+        <v>4.5494</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0477</v>
+        <v>0.0319</v>
       </c>
       <c r="J71" t="n">
-        <v>1.0971</v>
+        <v>0.7337</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>2.04</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6427</v>
+        <v>1.6849</v>
       </c>
       <c r="J72" t="n">
-        <v>47.6383</v>
+        <v>48.8621</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5621</v>
+        <v>0.5554</v>
       </c>
       <c r="J73" t="n">
-        <v>16.3009</v>
+        <v>16.1066</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.08</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2523</v>
+        <v>0.2218</v>
       </c>
       <c r="J74" t="n">
-        <v>7.3167</v>
+        <v>6.4322</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2723</v>
+        <v>-0.2345</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.8967</v>
+        <v>-6.8005</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.84</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.4983</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.5382</v>
+        <v>-14.4507</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.19</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4199</v>
+        <v>0.3638</v>
       </c>
       <c r="J77" t="n">
-        <v>12.1771</v>
+        <v>10.5502</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3859</v>
+        <v>0.3302</v>
       </c>
       <c r="J78" t="n">
-        <v>11.1911</v>
+        <v>9.575799999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.91</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1339</v>
+        <v>-0.115</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.8831</v>
+        <v>-3.335</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1454</v>
+        <v>-0.126</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.2166</v>
+        <v>-3.654</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3088</v>
+        <v>-0.2913</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.9552</v>
+        <v>-8.447699999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.62</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1215</v>
+        <v>1.1147</v>
       </c>
       <c r="J82" t="n">
-        <v>29.159</v>
+        <v>28.9822</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.14</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4109</v>
+        <v>0.3765</v>
       </c>
       <c r="J83" t="n">
-        <v>10.6834</v>
+        <v>9.789</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3118</v>
+        <v>0.2788</v>
       </c>
       <c r="J84" t="n">
-        <v>8.1068</v>
+        <v>7.2488</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.1</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3118</v>
+        <v>0.2788</v>
       </c>
       <c r="J85" t="n">
-        <v>8.1068</v>
+        <v>7.2488</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0916</v>
+        <v>-0.0707</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.3816</v>
+        <v>-1.8382</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.03</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1156</v>
+        <v>0.0859</v>
       </c>
       <c r="J87" t="n">
-        <v>3.0056</v>
+        <v>2.2334</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.03</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1156</v>
+        <v>0.0859</v>
       </c>
       <c r="J88" t="n">
-        <v>3.0056</v>
+        <v>2.2334</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.87</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1723</v>
+        <v>-0.1531</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.4798</v>
+        <v>-3.9806</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1829</v>
+        <v>-0.1634</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.7554</v>
+        <v>-4.2484</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.76</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2828</v>
+        <v>-0.264</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.3528</v>
+        <v>-6.864</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.51</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8619</v>
+        <v>0.8089</v>
       </c>
       <c r="J92" t="n">
-        <v>25.857</v>
+        <v>24.267</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.32</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5904</v>
+        <v>0.5315</v>
       </c>
       <c r="J93" t="n">
-        <v>17.712</v>
+        <v>15.945</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2132</v>
+        <v>0.1756</v>
       </c>
       <c r="J94" t="n">
-        <v>6.396</v>
+        <v>5.268</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1289</v>
+        <v>0.1016</v>
       </c>
       <c r="J95" t="n">
-        <v>3.867</v>
+        <v>3.048</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1835</v>
+        <v>-0.1635</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.505</v>
+        <v>-4.905</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.47</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1109</v>
+        <v>1.127</v>
       </c>
       <c r="J97" t="n">
-        <v>33.327</v>
+        <v>33.81</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.96</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1722</v>
+        <v>-0.1398</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.166</v>
+        <v>-4.194</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.95</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2039</v>
+        <v>-0.1686</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.117</v>
+        <v>-5.058</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3981</v>
+        <v>-0.3551</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.943</v>
+        <v>-10.653</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.84</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4973</v>
+        <v>-0.4551</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.919</v>
+        <v>-13.653</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.78</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2291</v>
+        <v>1.2315</v>
       </c>
       <c r="J102" t="n">
-        <v>34.4148</v>
+        <v>34.482</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.03</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1055</v>
+        <v>0.0776</v>
       </c>
       <c r="J103" t="n">
-        <v>2.954</v>
+        <v>2.1728</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1549</v>
+        <v>-0.1354</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.3372</v>
+        <v>-3.7912</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3163</v>
+        <v>-0.2992</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.856400000000001</v>
+        <v>-8.377599999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.38</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6199</v>
+        <v>-0.6402</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.3572</v>
+        <v>-17.9256</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.59</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2376</v>
+        <v>1.2554</v>
       </c>
       <c r="J107" t="n">
-        <v>34.6528</v>
+        <v>35.1512</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6792</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>19.0176</v>
+        <v>18.1076</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4839</v>
+        <v>0.447</v>
       </c>
       <c r="J109" t="n">
-        <v>13.5492</v>
+        <v>12.516</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="J110" t="n">
-        <v>0.952</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.75</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7301</v>
+        <v>-0.7024</v>
       </c>
       <c r="J111" t="n">
-        <v>-20.4428</v>
+        <v>-19.6672</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.68</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3236</v>
+        <v>1.3442</v>
       </c>
       <c r="J112" t="n">
-        <v>31.7664</v>
+        <v>32.2608</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.42</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9664</v>
+        <v>0.9601</v>
       </c>
       <c r="J113" t="n">
-        <v>23.1936</v>
+        <v>23.0424</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.3</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7398</v>
+        <v>0.7164</v>
       </c>
       <c r="J114" t="n">
-        <v>17.7552</v>
+        <v>17.1936</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.18</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4897</v>
+        <v>0.4584</v>
       </c>
       <c r="J115" t="n">
-        <v>11.7528</v>
+        <v>11.0016</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.86</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4971</v>
+        <v>-0.46</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.9304</v>
+        <v>-11.04</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.32</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.6818</v>
       </c>
       <c r="J117" t="n">
-        <v>17.2128</v>
+        <v>16.3632</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.98</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0181</v>
+        <v>-0.0104</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.4344</v>
+        <v>-0.2496</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.58</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4341</v>
+        <v>-0.4256</v>
       </c>
       <c r="J119" t="n">
-        <v>-10.4184</v>
+        <v>-10.2144</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4605</v>
+        <v>-0.4547</v>
       </c>
       <c r="J120" t="n">
-        <v>-11.052</v>
+        <v>-10.9128</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.5</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5041</v>
+        <v>-0.5036</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.0984</v>
+        <v>-12.0864</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7368</v>
+        <v>0.6822</v>
       </c>
       <c r="J122" t="n">
-        <v>22.104</v>
+        <v>20.466</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.06</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1704</v>
+        <v>0.1332</v>
       </c>
       <c r="J123" t="n">
-        <v>5.112</v>
+        <v>3.996</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.89</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1581</v>
+        <v>-0.1381</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.743</v>
+        <v>-4.143</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.84</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2117</v>
+        <v>-0.1911</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.351</v>
+        <v>-5.733</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2423</v>
+        <v>-0.2221</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.269</v>
+        <v>-6.663</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.37</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9135</v>
+        <v>0.8968</v>
       </c>
       <c r="J127" t="n">
-        <v>27.405</v>
+        <v>26.904</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5794</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>17.382</v>
+        <v>16.254</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.19</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.4964</v>
       </c>
       <c r="J129" t="n">
-        <v>16.044</v>
+        <v>14.892</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0648</v>
       </c>
       <c r="J130" t="n">
-        <v>2.463</v>
+        <v>1.944</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.8</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6109</v>
+        <v>-0.5743</v>
       </c>
       <c r="J131" t="n">
-        <v>-18.327</v>
+        <v>-17.229</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.37</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6998</v>
+        <v>0.6428</v>
       </c>
       <c r="J132" t="n">
-        <v>19.5944</v>
+        <v>17.9984</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2491</v>
+        <v>0.2032</v>
       </c>
       <c r="J133" t="n">
-        <v>6.9748</v>
+        <v>5.6896</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.05</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1452</v>
+        <v>0.1121</v>
       </c>
       <c r="J134" t="n">
-        <v>4.0656</v>
+        <v>3.1388</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.96</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.074</v>
+        <v>-0.0593</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.072</v>
+        <v>-1.6604</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.62</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4213</v>
+        <v>-0.4135</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.7964</v>
+        <v>-11.578</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.31</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7865</v>
+        <v>0.7595</v>
       </c>
       <c r="J137" t="n">
-        <v>22.022</v>
+        <v>21.266</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.17</v>
       </c>
       <c r="I138" t="n">
-        <v>0.486</v>
+        <v>0.4482</v>
       </c>
       <c r="J138" t="n">
-        <v>13.608</v>
+        <v>12.5496</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3195</v>
+        <v>0.2846</v>
       </c>
       <c r="J139" t="n">
-        <v>8.946</v>
+        <v>7.9688</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2664</v>
+        <v>0.2337</v>
       </c>
       <c r="J140" t="n">
-        <v>7.4592</v>
+        <v>6.5436</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.04</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1482</v>
+        <v>0.1235</v>
       </c>
       <c r="J141" t="n">
-        <v>4.1496</v>
+        <v>3.458</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.83</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4864</v>
+        <v>1.5169</v>
       </c>
       <c r="J142" t="n">
-        <v>32.7008</v>
+        <v>33.3718</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.37</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8619</v>
+        <v>0.8511</v>
       </c>
       <c r="J143" t="n">
-        <v>18.9618</v>
+        <v>18.7242</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.36</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8312</v>
       </c>
       <c r="J144" t="n">
-        <v>18.5504</v>
+        <v>18.2864</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.24</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6039</v>
+        <v>0.5788</v>
       </c>
       <c r="J145" t="n">
-        <v>13.2858</v>
+        <v>12.7336</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.21</v>
       </c>
       <c r="I146" t="n">
-        <v>0.5393</v>
+        <v>0.5115</v>
       </c>
       <c r="J146" t="n">
-        <v>11.8646</v>
+        <v>11.253</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.86</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.1544</v>
+        <v>-0.1382</v>
       </c>
       <c r="J147" t="n">
-        <v>-3.3968</v>
+        <v>-3.0404</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.75</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2697</v>
+        <v>-0.2559</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.9334</v>
+        <v>-5.6298</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2793</v>
+        <v>-0.2657</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.1446</v>
+        <v>-5.8454</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4038</v>
+        <v>-0.3934</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.883599999999999</v>
+        <v>-8.6548</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.47</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5182</v>
+        <v>-0.5187</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.4004</v>
+        <v>-11.4114</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.16</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3734</v>
+        <v>0.3184</v>
       </c>
       <c r="J152" t="n">
-        <v>9.335000000000001</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.04</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1309</v>
+        <v>0.0987</v>
       </c>
       <c r="J153" t="n">
-        <v>3.2725</v>
+        <v>2.4675</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0961</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.4025</v>
+        <v>-2.005</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.93</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1084</v>
+        <v>-0.0915</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.71</v>
+        <v>-2.2875</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.73</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3161</v>
+        <v>-0.299</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.9025</v>
+        <v>-7.475</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.27</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7133</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>17.8325</v>
+        <v>17.0225</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.15</v>
       </c>
       <c r="I158" t="n">
-        <v>0.446</v>
+        <v>0.4062</v>
       </c>
       <c r="J158" t="n">
-        <v>11.15</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3982</v>
+        <v>0.359</v>
       </c>
       <c r="J159" t="n">
-        <v>9.955</v>
+        <v>8.975</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0157</v>
+        <v>-0.0111</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.3925</v>
+        <v>-0.2775</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.95</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.219</v>
+        <v>-0.182</v>
       </c>
       <c r="J161" t="n">
-        <v>-5.475</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.54</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1337</v>
+        <v>1.1473</v>
       </c>
       <c r="J162" t="n">
-        <v>26.0751</v>
+        <v>26.3879</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.4</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9242</v>
+        <v>0.9144</v>
       </c>
       <c r="J163" t="n">
-        <v>21.2566</v>
+        <v>21.0312</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.34</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8123</v>
+        <v>0.7948</v>
       </c>
       <c r="J164" t="n">
-        <v>18.6829</v>
+        <v>18.2804</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.26</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6558</v>
+        <v>0.6309</v>
       </c>
       <c r="J165" t="n">
-        <v>15.0834</v>
+        <v>14.5107</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.11</v>
       </c>
       <c r="I166" t="n">
-        <v>0.3151</v>
+        <v>0.2832</v>
       </c>
       <c r="J166" t="n">
-        <v>7.2473</v>
+        <v>6.5136</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.13</v>
       </c>
       <c r="I167" t="n">
-        <v>0.345</v>
+        <v>0.2941</v>
       </c>
       <c r="J167" t="n">
-        <v>7.935</v>
+        <v>6.7643</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3255</v>
+        <v>0.2755</v>
       </c>
       <c r="J168" t="n">
-        <v>7.4865</v>
+        <v>6.3365</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.72</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3159</v>
+        <v>-0.2987</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.2657</v>
+        <v>-6.8701</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3345</v>
+        <v>-0.3183</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.6935</v>
+        <v>-7.3209</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.65</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3801</v>
+        <v>-0.3671</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.7423</v>
+        <v>-8.443300000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.07</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2511</v>
+        <v>0.2117</v>
       </c>
       <c r="J172" t="n">
-        <v>6.0264</v>
+        <v>5.0808</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.92</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1021</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.4504</v>
+        <v>-2.1096</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3345</v>
+        <v>-0.319</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.028</v>
+        <v>-7.656</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.61</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4067</v>
+        <v>-0.3957</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.7608</v>
+        <v>-9.4968</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.61</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4067</v>
+        <v>-0.3957</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.7608</v>
+        <v>-9.4968</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.53</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1272</v>
+        <v>1.14</v>
       </c>
       <c r="J177" t="n">
-        <v>27.0528</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.4</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9306</v>
+        <v>0.9197</v>
       </c>
       <c r="J178" t="n">
-        <v>22.3344</v>
+        <v>22.0728</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.3</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7396</v>
+        <v>0.7163</v>
       </c>
       <c r="J179" t="n">
-        <v>17.7504</v>
+        <v>17.1912</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7204</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>17.2896</v>
+        <v>16.7064</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.93</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3123</v>
+        <v>-0.2749</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.4952</v>
+        <v>-6.5976</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.57</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2229</v>
+        <v>1.2413</v>
       </c>
       <c r="J182" t="n">
-        <v>35.4641</v>
+        <v>35.9977</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.3</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7731</v>
+        <v>0.7447</v>
       </c>
       <c r="J183" t="n">
-        <v>22.4199</v>
+        <v>21.5963</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3966</v>
+        <v>0.358</v>
       </c>
       <c r="J184" t="n">
-        <v>11.5014</v>
+        <v>10.382</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.78</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.6554</v>
+        <v>-0.6213</v>
       </c>
       <c r="J185" t="n">
-        <v>-19.0066</v>
+        <v>-18.0177</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6554</v>
+        <v>-0.6213</v>
       </c>
       <c r="J186" t="n">
-        <v>-19.0066</v>
+        <v>-18.0177</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4371</v>
+        <v>0.3795</v>
       </c>
       <c r="J187" t="n">
-        <v>12.6759</v>
+        <v>11.0055</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.07</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1939</v>
+        <v>0.1535</v>
       </c>
       <c r="J188" t="n">
-        <v>5.6231</v>
+        <v>4.4515</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.04</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1266</v>
+        <v>0.0955</v>
       </c>
       <c r="J189" t="n">
-        <v>3.6714</v>
+        <v>2.7695</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0247</v>
+        <v>-0.0179</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.7163</v>
+        <v>-0.5191</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4096</v>
+        <v>-0.4002</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.8784</v>
+        <v>-11.6058</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.08</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2391</v>
+        <v>0.1946</v>
       </c>
       <c r="J192" t="n">
-        <v>5.9775</v>
+        <v>4.865</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.93</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1029</v>
+        <v>-0.0883</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.5725</v>
+        <v>-2.2075</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1151</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.8775</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.8</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.241</v>
+        <v>-0.2216</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.025</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.67</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3637</v>
+        <v>-0.3494</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.092499999999999</v>
+        <v>-8.734999999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.43</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9974</v>
+        <v>0.9942</v>
       </c>
       <c r="J197" t="n">
-        <v>24.935</v>
+        <v>24.855</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.42</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9806</v>
+        <v>0.9746</v>
       </c>
       <c r="J198" t="n">
-        <v>24.515</v>
+        <v>24.365</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.31</v>
       </c>
       <c r="I199" t="n">
-        <v>0.7701</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>19.2525</v>
+        <v>18.6125</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3334</v>
+        <v>0.3005</v>
       </c>
       <c r="J200" t="n">
-        <v>8.335000000000001</v>
+        <v>7.5125</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.605</v>
+        <v>-0.5704</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.125</v>
+        <v>-14.26</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0083</v>
+        <v>0.017</v>
       </c>
       <c r="J202" t="n">
-        <v>0.1909</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.77</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2599</v>
+        <v>-0.2435</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.9777</v>
+        <v>-5.6005</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2688</v>
+        <v>-0.2524</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.1824</v>
+        <v>-5.8052</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.65</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.369</v>
+        <v>-0.3554</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.487</v>
+        <v>-8.174200000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.369</v>
+        <v>-0.3554</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.487</v>
+        <v>-8.174200000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1557</v>
+        <v>1.1691</v>
       </c>
       <c r="J207" t="n">
-        <v>26.5811</v>
+        <v>26.8893</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.39</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9139</v>
+        <v>0.9008</v>
       </c>
       <c r="J208" t="n">
-        <v>21.0197</v>
+        <v>20.7184</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.23</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="J209" t="n">
-        <v>13.8</v>
+        <v>13.133</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.19</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5133</v>
+        <v>0.4822</v>
       </c>
       <c r="J210" t="n">
-        <v>11.8059</v>
+        <v>11.0906</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1243</v>
+        <v>0.1006</v>
       </c>
       <c r="J211" t="n">
-        <v>2.8589</v>
+        <v>2.3138</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.09</v>
       </c>
       <c r="I212" t="n">
-        <v>1.7823</v>
+        <v>1.8389</v>
       </c>
       <c r="J212" t="n">
-        <v>33.8637</v>
+        <v>34.9391</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.52</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0917</v>
+        <v>1.1074</v>
       </c>
       <c r="J213" t="n">
-        <v>20.7423</v>
+        <v>21.0406</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.36</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8369</v>
+        <v>0.8267</v>
       </c>
       <c r="J214" t="n">
-        <v>15.9011</v>
+        <v>15.7073</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.28</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6795</v>
+        <v>0.6592</v>
       </c>
       <c r="J215" t="n">
-        <v>12.9105</v>
+        <v>12.5248</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.02</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0273</v>
+        <v>0.0074</v>
       </c>
       <c r="J216" t="n">
-        <v>0.5187</v>
+        <v>0.1406</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.88</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1358</v>
+        <v>-0.1198</v>
       </c>
       <c r="J217" t="n">
-        <v>-2.5802</v>
+        <v>-2.2762</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.75</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2725</v>
+        <v>-0.2582</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.1775</v>
+        <v>-4.9058</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.71</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3092</v>
+        <v>-0.2952</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.8748</v>
+        <v>-5.6088</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.7</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3177</v>
+        <v>-0.3039</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.0363</v>
+        <v>-5.7741</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.48</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.512</v>
+        <v>-0.5118</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.728</v>
+        <v>-9.7242</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.45</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0514</v>
+        <v>1.0574</v>
       </c>
       <c r="J222" t="n">
-        <v>26.285</v>
+        <v>26.435</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.322</v>
+        <v>0.2861</v>
       </c>
       <c r="J223" t="n">
-        <v>8.050000000000001</v>
+        <v>7.1525</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.07</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2415</v>
+        <v>0.2095</v>
       </c>
       <c r="J224" t="n">
-        <v>6.0375</v>
+        <v>5.2375</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0196</v>
+        <v>-0.0146</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.49</v>
+        <v>-0.365</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.0794</v>
+        <v>-0.0588</v>
       </c>
       <c r="J226" t="n">
-        <v>-1.985</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.9</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3331</v>
+        <v>1.3385</v>
       </c>
       <c r="J227" t="n">
-        <v>33.3275</v>
+        <v>33.4625</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.01</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0433</v>
+        <v>0.0293</v>
       </c>
       <c r="J228" t="n">
-        <v>1.0825</v>
+        <v>0.7325</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.83</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2222</v>
+        <v>-0.2017</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.555</v>
+        <v>-5.0425</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.67</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.375</v>
+        <v>-0.3625</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.375</v>
+        <v>-9.0625</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4459</v>
+        <v>-0.4407</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.1475</v>
+        <v>-11.0175</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.38</v>
       </c>
       <c r="I232" t="n">
-        <v>0.93</v>
+        <v>0.9153</v>
       </c>
       <c r="J232" t="n">
-        <v>24.18</v>
+        <v>23.7978</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.3</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7689</v>
+        <v>0.7405</v>
       </c>
       <c r="J233" t="n">
-        <v>19.9914</v>
+        <v>19.253</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.23</v>
       </c>
       <c r="I234" t="n">
-        <v>0.621</v>
+        <v>0.5851</v>
       </c>
       <c r="J234" t="n">
-        <v>16.146</v>
+        <v>15.2126</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.15</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4417</v>
+        <v>0.4034</v>
       </c>
       <c r="J235" t="n">
-        <v>11.4842</v>
+        <v>10.4884</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.58</v>
       </c>
       <c r="I236" t="n">
-        <v>-1.0795</v>
+        <v>-1.0899</v>
       </c>
       <c r="J236" t="n">
-        <v>-28.067</v>
+        <v>-28.3374</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.33</v>
       </c>
       <c r="I237" t="n">
-        <v>0.645</v>
+        <v>0.587</v>
       </c>
       <c r="J237" t="n">
-        <v>16.77</v>
+        <v>15.262</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2722</v>
+        <v>0.2239</v>
       </c>
       <c r="J238" t="n">
-        <v>7.0772</v>
+        <v>5.8214</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.07</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1919</v>
+        <v>0.1519</v>
       </c>
       <c r="J239" t="n">
-        <v>4.9894</v>
+        <v>3.9494</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.79</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2621</v>
+        <v>-0.2425</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.8146</v>
+        <v>-6.305</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3567</v>
+        <v>-0.3426</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.2742</v>
+        <v>-8.9076</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.29</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5985</v>
+        <v>0.5416</v>
       </c>
       <c r="J242" t="n">
-        <v>17.3565</v>
+        <v>15.7064</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0509</v>
+        <v>0.0342</v>
       </c>
       <c r="J243" t="n">
-        <v>1.4761</v>
+        <v>0.9918</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.96</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0693</v>
+        <v>-0.0565</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.0097</v>
+        <v>-1.6385</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.78</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2668</v>
+        <v>-0.2474</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.7372</v>
+        <v>-7.1746</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.68</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3609</v>
+        <v>-0.3467</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.4661</v>
+        <v>-10.0543</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7689</v>
+        <v>0.7405</v>
       </c>
       <c r="J247" t="n">
-        <v>22.2981</v>
+        <v>21.4745</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.19</v>
       </c>
       <c r="I248" t="n">
-        <v>0.533</v>
+        <v>0.4949</v>
       </c>
       <c r="J248" t="n">
-        <v>15.457</v>
+        <v>14.3521</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.17</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4878</v>
+        <v>0.4494</v>
       </c>
       <c r="J249" t="n">
-        <v>14.1462</v>
+        <v>13.0326</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.05</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1818</v>
+        <v>0.1541</v>
       </c>
       <c r="J250" t="n">
-        <v>5.2722</v>
+        <v>4.4689</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.284</v>
+        <v>-0.2438</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.236000000000001</v>
+        <v>-7.0702</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.94</v>
       </c>
       <c r="I252" t="n">
-        <v>1.6146</v>
+        <v>1.6553</v>
       </c>
       <c r="J252" t="n">
-        <v>35.5212</v>
+        <v>36.4166</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.45</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9975000000000001</v>
+        <v>1.0016</v>
       </c>
       <c r="J253" t="n">
-        <v>21.945</v>
+        <v>22.0352</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.45</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9975000000000001</v>
+        <v>1.0016</v>
       </c>
       <c r="J254" t="n">
-        <v>21.945</v>
+        <v>22.0352</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.21</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5367</v>
+        <v>0.5089</v>
       </c>
       <c r="J255" t="n">
-        <v>11.8074</v>
+        <v>11.1958</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.05</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1341</v>
+        <v>0.1061</v>
       </c>
       <c r="J256" t="n">
-        <v>2.9502</v>
+        <v>2.3342</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.91</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1102</v>
+        <v>-0.0955</v>
       </c>
       <c r="J257" t="n">
-        <v>-2.4244</v>
+        <v>-2.101</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1223</v>
+        <v>-0.1073</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.6906</v>
+        <v>-2.3606</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.72</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3045</v>
+        <v>-0.2886</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.699</v>
+        <v>-6.3492</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.72</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3045</v>
+        <v>-0.2886</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.699</v>
+        <v>-6.3492</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.53</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4746</v>
+        <v>-0.4702</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.4412</v>
+        <v>-10.3444</v>
       </c>
     </row>
   </sheetData>
